--- a/research/traditional_assets/database/data/south_korea/south_korea_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_brokerage_investment_banking.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1745</v>
+        <v>0.1885</v>
       </c>
       <c r="E2">
-        <v>0.347</v>
+        <v>0.1495</v>
       </c>
       <c r="G2">
-        <v>0.02740924653275746</v>
+        <v>0.02234522985960075</v>
       </c>
       <c r="H2">
-        <v>0.02737042225888192</v>
+        <v>0.02231954889089072</v>
       </c>
       <c r="I2">
-        <v>0.03089223984282387</v>
+        <v>0.01300970004031315</v>
       </c>
       <c r="J2">
-        <v>0.02300596471463042</v>
+        <v>0.009591040104876226</v>
       </c>
       <c r="K2">
-        <v>6777.22</v>
+        <v>3209.013</v>
       </c>
       <c r="L2">
-        <v>0.09363724035403317</v>
+        <v>0.03194207846630866</v>
       </c>
       <c r="M2">
-        <v>1186.1035</v>
+        <v>1398.0579</v>
       </c>
       <c r="N2">
-        <v>0.05023861258651215</v>
+        <v>0.08131694847231674</v>
       </c>
       <c r="O2">
-        <v>0.1750132797813853</v>
+        <v>0.4356660131947113</v>
       </c>
       <c r="P2">
-        <v>980.0165000000001</v>
+        <v>1126.5679</v>
       </c>
       <c r="Q2">
-        <v>0.04150958940083187</v>
+        <v>0.06552594415071512</v>
       </c>
       <c r="R2">
-        <v>0.1446044985997208</v>
+        <v>0.3510636759651644</v>
       </c>
       <c r="S2">
-        <v>206.087</v>
+        <v>271.49</v>
       </c>
       <c r="T2">
-        <v>0.173751278872375</v>
+        <v>0.1941908128411563</v>
       </c>
       <c r="U2">
-        <v>29374.511</v>
+        <v>18937.4</v>
       </c>
       <c r="V2">
-        <v>1.244187103441849</v>
+        <v>1.1014791161365</v>
       </c>
       <c r="W2">
-        <v>0.1787467768223233</v>
+        <v>0.06611676400469138</v>
       </c>
       <c r="X2">
-        <v>0.1509182908300087</v>
+        <v>0.3230365993696487</v>
       </c>
       <c r="Y2">
-        <v>0.02782848599231461</v>
+        <v>-0.2569198353649573</v>
       </c>
       <c r="Z2">
-        <v>0.3837262214932681</v>
+        <v>0.4779129947889176</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03594359072760375</v>
+        <v>0.06382651427999006</v>
       </c>
       <c r="AC2">
-        <v>-0.03593793273297068</v>
+        <v>-0.06382651427999006</v>
       </c>
       <c r="AD2">
-        <v>199936</v>
+        <v>177761.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>199936</v>
+        <v>177761.9</v>
       </c>
       <c r="AG2">
-        <v>170561.489</v>
+        <v>158824.5</v>
       </c>
       <c r="AH2">
-        <v>0.8943865541406801</v>
+        <v>0.9118117756646932</v>
       </c>
       <c r="AI2">
-        <v>0.8132997549963776</v>
+        <v>0.811086340349654</v>
       </c>
       <c r="AJ2">
-        <v>0.8784091677099959</v>
+        <v>0.9023237501789597</v>
       </c>
       <c r="AK2">
-        <v>0.787963599818162</v>
+        <v>0.7932190235321969</v>
       </c>
       <c r="AL2">
-        <v>9.449999999999999</v>
+        <v>133.05</v>
       </c>
       <c r="AM2">
-        <v>2.560999999999999</v>
+        <v>130.416</v>
       </c>
       <c r="AN2">
-        <v>86.12362696532415</v>
+        <v>127.8678607394619</v>
       </c>
       <c r="AO2">
-        <v>236.6031746031746</v>
+        <v>9.823374671176248</v>
       </c>
       <c r="AP2">
-        <v>73.47038078828344</v>
+        <v>114.2457919723781</v>
       </c>
       <c r="AQ2">
-        <v>873.0573994533389</v>
+        <v>10.02177646914489</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daou Technology Inc. (KOSE:A023590)</t>
+          <t>Daou Data Corp. (KOSDAQ:A032190)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.2538103822138621</v>
+        <v>0.1663635576340175</v>
       </c>
       <c r="H3">
-        <v>0.2530762598949761</v>
+        <v>0.1663635576340175</v>
       </c>
       <c r="I3">
-        <v>0.2881364788254043</v>
+        <v>0.1064057042233192</v>
       </c>
       <c r="J3">
-        <v>0.1924977428680044</v>
+        <v>0.07647008858732103</v>
       </c>
       <c r="K3">
-        <v>296</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L3">
-        <v>0.0773310343025838</v>
+        <v>0.009295343667907971</v>
       </c>
       <c r="M3">
-        <v>18.3159</v>
+        <v>8.0047</v>
       </c>
       <c r="N3">
-        <v>0.02210463432295438</v>
+        <v>0.008537436006825938</v>
       </c>
       <c r="O3">
-        <v>0.06187804054054054</v>
+        <v>0.1242965838509317</v>
       </c>
       <c r="P3">
-        <v>18.3159</v>
+        <v>8.0047</v>
       </c>
       <c r="Q3">
-        <v>0.02210463432295438</v>
+        <v>0.008537436006825938</v>
       </c>
       <c r="R3">
-        <v>0.06187804054054054</v>
+        <v>0.1242965838509317</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1305.6</v>
+        <v>1144.2</v>
       </c>
       <c r="V3">
-        <v>1.5756698044895</v>
+        <v>1.220349829351536</v>
       </c>
       <c r="W3">
-        <v>0.2259541984732824</v>
+        <v>0.08262766230433669</v>
       </c>
       <c r="X3">
-        <v>0.3204009275242926</v>
+        <v>0.4527162972115989</v>
       </c>
       <c r="Y3">
-        <v>-0.09444672905101018</v>
+        <v>-0.3700886349072622</v>
       </c>
       <c r="Z3">
-        <v>0.2753998575406333</v>
+        <v>0.3695375047337625</v>
       </c>
       <c r="AA3">
-        <v>0.05301385096274186</v>
+        <v>0.02825856572332838</v>
       </c>
       <c r="AB3">
-        <v>0.03594603994220191</v>
+        <v>0.06353623527060537</v>
       </c>
       <c r="AC3">
-        <v>0.01706781102053995</v>
+        <v>-0.03527766954727699</v>
       </c>
       <c r="AD3">
-        <v>15435.4</v>
+        <v>15506.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15435.4</v>
+        <v>15506.8</v>
       </c>
       <c r="AG3">
-        <v>14129.8</v>
+        <v>14362.6</v>
       </c>
       <c r="AH3">
-        <v>0.9490531234628627</v>
+        <v>0.9429836296854858</v>
       </c>
       <c r="AI3">
-        <v>0.8053028089653157</v>
+        <v>0.8117808419972568</v>
       </c>
       <c r="AJ3">
-        <v>0.9446063750133704</v>
+        <v>0.9387197552973163</v>
       </c>
       <c r="AK3">
-        <v>0.7910713485913916</v>
+        <v>0.7997883951442253</v>
       </c>
       <c r="AL3">
-        <v>6</v>
+        <v>127.8</v>
       </c>
       <c r="AM3">
-        <v>5.651</v>
+        <v>126.12</v>
       </c>
       <c r="AN3">
-        <v>13.53982456140351</v>
+        <v>19.66370783667258</v>
       </c>
       <c r="AO3">
-        <v>183.8166666666667</v>
+        <v>5.768388106416276</v>
       </c>
       <c r="AP3">
-        <v>12.39456140350877</v>
+        <v>18.21278214557443</v>
       </c>
       <c r="AQ3">
-        <v>195.1689966377633</v>
+        <v>5.845226768157311</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Daou Data Corp. (KOSDAQ:A032190)</t>
+          <t>Daou Technology Inc. (KOSE:A023590)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,121 +850,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>0.489</v>
       </c>
       <c r="E4">
-        <v>0.419</v>
+        <v>0.223</v>
       </c>
       <c r="G4">
-        <v>0.2413053324116231</v>
+        <v>0.1671021632041122</v>
       </c>
       <c r="H4">
-        <v>0.2413053324116231</v>
+        <v>0.166707462595233</v>
       </c>
       <c r="I4">
-        <v>0.2700769945889251</v>
+        <v>0.08717070036410365</v>
       </c>
       <c r="J4">
-        <v>0.1761041155538466</v>
+        <v>0.06525803807367775</v>
       </c>
       <c r="K4">
-        <v>126.6</v>
+        <v>198.7</v>
       </c>
       <c r="L4">
-        <v>0.03017806488522323</v>
+        <v>0.03039806627298595</v>
       </c>
       <c r="M4">
-        <v>8.119599999999998</v>
+        <v>19.4776</v>
       </c>
       <c r="N4">
-        <v>0.01671387402223137</v>
+        <v>0.02972318022279872</v>
       </c>
       <c r="O4">
-        <v>0.06413586097946286</v>
+        <v>0.09802516356316056</v>
       </c>
       <c r="P4">
-        <v>8.119599999999998</v>
+        <v>18.0576</v>
       </c>
       <c r="Q4">
-        <v>0.01671387402223137</v>
+        <v>0.02755623378605219</v>
       </c>
       <c r="R4">
-        <v>0.06413586097946286</v>
+        <v>0.09087871162556618</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.420000000000002</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.07290425925165325</v>
       </c>
       <c r="U4">
-        <v>1392.4</v>
+        <v>1052.8</v>
       </c>
       <c r="V4">
-        <v>2.866200082338411</v>
+        <v>1.606592400427285</v>
       </c>
       <c r="W4">
-        <v>0.198962753418199</v>
+        <v>0.1238237676824328</v>
       </c>
       <c r="X4">
-        <v>0.6538356513712906</v>
+        <v>0.6102551585891851</v>
       </c>
       <c r="Y4">
-        <v>-0.4548728979530917</v>
+        <v>-0.4864313909067522</v>
       </c>
       <c r="Z4">
-        <v>0.3153641448159731</v>
+        <v>0.4166146158650844</v>
       </c>
       <c r="AA4">
-        <v>0.05553692380021214</v>
+        <v>0.02718745246417431</v>
       </c>
       <c r="AB4">
-        <v>0.03933862153903205</v>
+        <v>0.06343242804314</v>
       </c>
       <c r="AC4">
-        <v>0.01619830226118009</v>
+        <v>-0.03624497557896569</v>
       </c>
       <c r="AD4">
-        <v>19640.6</v>
+        <v>15295.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>19640.6</v>
+        <v>15295.4</v>
       </c>
       <c r="AG4">
-        <v>18248.2</v>
+        <v>14242.6</v>
       </c>
       <c r="AH4">
-        <v>0.975862548692265</v>
+        <v>0.9589171635100654</v>
       </c>
       <c r="AI4">
-        <v>0.8310807951727698</v>
+        <v>0.8163162922757524</v>
       </c>
       <c r="AJ4">
-        <v>0.9740685384861749</v>
+        <v>0.9560139348498782</v>
       </c>
       <c r="AK4">
-        <v>0.8205052112840712</v>
+        <v>0.8053810442030502</v>
       </c>
       <c r="AL4">
-        <v>3.45</v>
+        <v>5.25</v>
       </c>
       <c r="AM4">
-        <v>-3.09</v>
+        <v>4.296</v>
       </c>
       <c r="AN4">
-        <v>16.62344477359289</v>
+        <v>25.42453457446808</v>
       </c>
       <c r="AO4">
-        <v>328.4057971014493</v>
+        <v>108.5333333333333</v>
       </c>
       <c r="AP4">
-        <v>15.44494286923402</v>
+        <v>23.67453457446808</v>
       </c>
       <c r="AQ4">
-        <v>-366.6666666666667</v>
+        <v>132.635009310987</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yuhwa Securities co.,ltd. (KOSE:A003460)</t>
+          <t>DB Financial Investment Co., Ltd. (KOSE:A016610)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00084</v>
+        <v>0.112</v>
       </c>
       <c r="E5">
-        <v>-0.0453</v>
+        <v>0.106</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1002,82 +1002,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>7.11</v>
+        <v>21.3</v>
       </c>
       <c r="L5">
-        <v>0.3864130434782609</v>
+        <v>0.02075214341387373</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>17.1884</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1299198790627362</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.8069671361502346</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>14.1984</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1073197278911564</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.6665915492957745</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.99</v>
+      </c>
+      <c r="T5">
+        <v>0.173954527472016</v>
       </c>
       <c r="U5">
-        <v>0.461</v>
+        <v>373</v>
       </c>
       <c r="V5">
-        <v>0.004349056603773585</v>
+        <v>2.819349962207105</v>
       </c>
       <c r="W5">
-        <v>0.01850598646538261</v>
+        <v>0.0281336679434685</v>
       </c>
       <c r="X5">
-        <v>0.05250393339846021</v>
+        <v>0.5126577097131007</v>
       </c>
       <c r="Y5">
-        <v>-0.0339979469330776</v>
+        <v>-0.4845240417696322</v>
       </c>
       <c r="Z5">
-        <v>0.0364529677470481</v>
+        <v>0.2848816231369175</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0357441546681117</v>
+        <v>0.06348846829580546</v>
       </c>
       <c r="AC5">
-        <v>-0.0357441546681117</v>
+        <v>-0.06348846829580546</v>
       </c>
       <c r="AD5">
-        <v>117.9</v>
+        <v>2530.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>117.9</v>
+        <v>2530.5</v>
       </c>
       <c r="AG5">
-        <v>117.439</v>
+        <v>2157.5</v>
       </c>
       <c r="AH5">
-        <v>0.5265743635551585</v>
+        <v>0.9503154574132492</v>
       </c>
       <c r="AI5">
-        <v>0.223253171747775</v>
+        <v>0.7728605460875939</v>
       </c>
       <c r="AJ5">
-        <v>0.5255975903937987</v>
+        <v>0.942222028124727</v>
       </c>
       <c r="AK5">
-        <v>0.2225745253857278</v>
+        <v>0.7436577967737489</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1094,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sangsangin Investment &amp; Securities Co.,Ltd. (KOSE:A001290)</t>
+          <t>Eugene Investment &amp; Securities Co.,Ltd. (KOSE:A001200)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,7 +1106,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0867</v>
+        <v>0.214</v>
+      </c>
+      <c r="E6">
+        <v>0.00045</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1118,82 +1124,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>5.81</v>
+        <v>36.7</v>
       </c>
       <c r="L6">
-        <v>0.1874193548387097</v>
+        <v>0.0294188376753507</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>8.9046</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.05238</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.2426321525885559</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>8.9046</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.05238</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.2426321525885559</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>2.85</v>
+        <v>500.7</v>
       </c>
       <c r="V6">
-        <v>0.03051391862955032</v>
+        <v>2.945294117647059</v>
       </c>
       <c r="W6">
-        <v>0.04074333800841515</v>
+        <v>0.04578343313373254</v>
       </c>
       <c r="X6">
-        <v>0.07322088351948858</v>
+        <v>0.4943631648769586</v>
       </c>
       <c r="Y6">
-        <v>-0.03247754551107343</v>
+        <v>-0.4485797317432261</v>
       </c>
       <c r="Z6">
-        <v>0.09328919650917847</v>
+        <v>0.3089324187117704</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03583254710150993</v>
+        <v>0.06350169136858931</v>
       </c>
       <c r="AC6">
-        <v>-0.03583254710150993</v>
+        <v>-0.06350169136858931</v>
       </c>
       <c r="AD6">
-        <v>230.4</v>
+        <v>3117.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>230.4</v>
+        <v>3117.3</v>
       </c>
       <c r="AG6">
-        <v>227.55</v>
+        <v>2616.6</v>
       </c>
       <c r="AH6">
-        <v>0.711550339715874</v>
+        <v>0.9482858272746632</v>
       </c>
       <c r="AI6">
-        <v>0.5844748858447488</v>
+        <v>0.8136615159741073</v>
       </c>
       <c r="AJ6">
-        <v>0.7089889390870852</v>
+        <v>0.9389937558314793</v>
       </c>
       <c r="AK6">
-        <v>0.5814488309697202</v>
+        <v>0.785647800630536</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1210,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOOKOOK Securities Co., Ltd. (KOSE:A001270)</t>
+          <t>Hyundai Motor Securities Co., Ltd. (KOSE:A001500)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,10 +1228,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0257</v>
+        <v>0.183</v>
       </c>
       <c r="E7">
-        <v>0.221</v>
+        <v>0.183</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,85 +1246,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>71.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="L7">
-        <v>0.1166123778501629</v>
+        <v>0.09923771880293619</v>
       </c>
       <c r="M7">
-        <v>9.231999999999999</v>
+        <v>17.6569</v>
       </c>
       <c r="N7">
-        <v>0.05050328227571115</v>
+        <v>0.07744254385964912</v>
       </c>
       <c r="O7">
-        <v>0.1289385474860335</v>
+        <v>0.2511650071123755</v>
       </c>
       <c r="P7">
-        <v>9.16</v>
+        <v>17.6569</v>
       </c>
       <c r="Q7">
-        <v>0.05010940919037199</v>
+        <v>0.07744254385964912</v>
       </c>
       <c r="R7">
-        <v>0.1279329608938548</v>
+        <v>0.2511650071123755</v>
       </c>
       <c r="S7">
-        <v>0.07199999999999918</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.007798960138648092</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>348.6</v>
+        <v>381.7</v>
       </c>
       <c r="V7">
-        <v>1.907002188183808</v>
+        <v>1.674122807017544</v>
       </c>
       <c r="W7">
-        <v>0.1565711786573365</v>
+        <v>0.07458094631869297</v>
       </c>
       <c r="X7">
-        <v>0.07984459788963987</v>
+        <v>0.4606036924916975</v>
       </c>
       <c r="Y7">
-        <v>0.07672658076769666</v>
+        <v>-0.3860227461730046</v>
       </c>
       <c r="Z7">
-        <v>0.2731681274191395</v>
+        <v>0.1439720347939192</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03584785398127846</v>
+        <v>0.06352915971619311</v>
       </c>
       <c r="AC7">
-        <v>-0.03584785398127846</v>
+        <v>-0.06352915971619311</v>
       </c>
       <c r="AD7">
-        <v>530.1</v>
+        <v>3848.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>530.1</v>
+        <v>3848.5</v>
       </c>
       <c r="AG7">
-        <v>181.5</v>
+        <v>3466.8</v>
       </c>
       <c r="AH7">
-        <v>0.7435825501472857</v>
+        <v>0.9440696676070158</v>
       </c>
       <c r="AI7">
-        <v>0.4899260628465804</v>
+        <v>0.8173689576076799</v>
       </c>
       <c r="AJ7">
-        <v>0.4982157562448531</v>
+        <v>0.9382916531341344</v>
       </c>
       <c r="AK7">
-        <v>0.2474775020452686</v>
+        <v>0.8012573092657223</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1332,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hanyang Securities Co. Ltd. (KOSE:A001750)</t>
+          <t>Kyobo Securities Co.,Ltd. (KOSE:A030610)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1341,10 +1350,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.342</v>
+        <v>0.407</v>
       </c>
       <c r="E8">
-        <v>0.64</v>
+        <v>0.0925</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1359,82 +1368,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>63</v>
+        <v>53.6</v>
       </c>
       <c r="L8">
-        <v>0.09839137904107451</v>
+        <v>0.01724970231390596</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>22.1328</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.08367788279773157</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.4129253731343284</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>22.1328</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.08367788279773157</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.4129253731343284</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>85</v>
+        <v>102.6</v>
       </c>
       <c r="V8">
-        <v>0.5062537224538416</v>
+        <v>0.3879017013232514</v>
       </c>
       <c r="W8">
-        <v>0.218978102189781</v>
+        <v>0.04589041095890411</v>
       </c>
       <c r="X8">
-        <v>0.09668832395257403</v>
+        <v>0.4097135449678069</v>
       </c>
       <c r="Y8">
-        <v>0.122289778237207</v>
+        <v>-0.3638231340089028</v>
       </c>
       <c r="Z8">
-        <v>0.3913933799932761</v>
+        <v>0.7238061961332402</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0358748363302813</v>
+        <v>0.0635802170827558</v>
       </c>
       <c r="AC8">
-        <v>-0.0358748363302813</v>
+        <v>-0.0635802170827558</v>
       </c>
       <c r="AD8">
-        <v>671.8</v>
+        <v>3883.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>671.8</v>
+        <v>3883.4</v>
       </c>
       <c r="AG8">
-        <v>586.8</v>
+        <v>3780.8</v>
       </c>
       <c r="AH8">
-        <v>0.8000476360604978</v>
+        <v>0.9362327924974084</v>
       </c>
       <c r="AI8">
-        <v>0.6541382667964946</v>
+        <v>0.7904013677440366</v>
       </c>
       <c r="AJ8">
-        <v>0.7775274943686233</v>
+        <v>0.9346154796924826</v>
       </c>
       <c r="AK8">
-        <v>0.6229299363057325</v>
+        <v>0.7859310688895356</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,7 +1463,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EBEST Investment &amp; Securities Co., Ltd. (KOSDAQ:A078020)</t>
+          <t>Korea Investment Holdings Co., Ltd. (KOSE:A071050)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1460,10 +1472,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.213</v>
+        <v>0.306</v>
       </c>
       <c r="E9">
-        <v>0.463</v>
+        <v>0.143</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1478,28 +1490,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>143.9</v>
+        <v>612.1</v>
       </c>
       <c r="L9">
-        <v>0.1037191869684302</v>
+        <v>0.04460069950451764</v>
       </c>
       <c r="M9">
-        <v>23.436</v>
+        <v>255.4</v>
       </c>
       <c r="N9">
-        <v>0.06757785467128027</v>
+        <v>0.1037367993501219</v>
       </c>
       <c r="O9">
-        <v>0.1628630993745657</v>
+        <v>0.417252082992975</v>
       </c>
       <c r="P9">
-        <v>23.436</v>
+        <v>255.4</v>
       </c>
       <c r="Q9">
-        <v>0.06757785467128027</v>
+        <v>0.1037367993501219</v>
       </c>
       <c r="R9">
-        <v>0.1628630993745657</v>
+        <v>0.417252082992975</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1508,55 +1520,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>47.5</v>
+        <v>8060.3</v>
       </c>
       <c r="V9">
-        <v>0.1369665513264129</v>
+        <v>3.273883021933388</v>
       </c>
       <c r="W9">
-        <v>0.2594662820050487</v>
+        <v>0.1024332284624138</v>
       </c>
       <c r="X9">
-        <v>0.1129832445648171</v>
+        <v>0.4046217062217985</v>
       </c>
       <c r="Y9">
-        <v>0.1464830374402316</v>
+        <v>-0.3021884777593847</v>
       </c>
       <c r="Z9">
-        <v>0.5800894761048627</v>
+        <v>0.4968287526427062</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03589161665084498</v>
+        <v>0.06358612427454154</v>
       </c>
       <c r="AC9">
-        <v>-0.03589161665084498</v>
+        <v>-0.06358612427454154</v>
       </c>
       <c r="AD9">
-        <v>1757.1</v>
+        <v>35605.9</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1757.1</v>
+        <v>35605.9</v>
       </c>
       <c r="AG9">
-        <v>1709.6</v>
+        <v>27545.6</v>
       </c>
       <c r="AH9">
-        <v>0.8351632682161699</v>
+        <v>0.9353260883841767</v>
       </c>
       <c r="AI9">
-        <v>0.6975663980308866</v>
+        <v>0.8656075266203141</v>
       </c>
       <c r="AJ9">
-        <v>0.8313557673604356</v>
+        <v>0.9179541182900331</v>
       </c>
       <c r="AK9">
-        <v>0.691753661892045</v>
+        <v>0.8328551084396363</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1573,7 +1585,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samsung Securities Co., Ltd. (KOSE:A016360)</t>
+          <t>Yuanta Securities Korea Co., Ltd. (KOSE:A003470)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1582,10 +1594,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.193</v>
-      </c>
-      <c r="E10">
-        <v>0.409</v>
+        <v>0.0876</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1600,28 +1609,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>802.6</v>
+        <v>-7.03</v>
       </c>
       <c r="L10">
-        <v>0.1059258281641811</v>
+        <v>-0.004295490651350361</v>
       </c>
       <c r="M10">
-        <v>166.098</v>
+        <v>26.2</v>
       </c>
       <c r="N10">
-        <v>0.0493165083135392</v>
+        <v>0.06730028255843822</v>
       </c>
       <c r="O10">
-        <v>0.2069499127834538</v>
+        <v>-3.726884779516358</v>
       </c>
       <c r="P10">
-        <v>166.098</v>
+        <v>26.2</v>
       </c>
       <c r="Q10">
-        <v>0.0493165083135392</v>
+        <v>0.06730028255843822</v>
       </c>
       <c r="R10">
-        <v>0.2069499127834538</v>
+        <v>-3.726884779516358</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1630,55 +1639,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>3123.5</v>
+        <v>595.4</v>
       </c>
       <c r="V10">
-        <v>0.9274049881235155</v>
+        <v>1.529411764705882</v>
       </c>
       <c r="W10">
-        <v>0.1797254629733301</v>
+        <v>-0.005283727921833898</v>
       </c>
       <c r="X10">
-        <v>0.140703703436935</v>
+        <v>0.3740118853991187</v>
       </c>
       <c r="Y10">
-        <v>0.03902175953639508</v>
+        <v>-0.3792956133209526</v>
       </c>
       <c r="Z10">
-        <v>0.3249407112929441</v>
+        <v>0.2675013484578546</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03590973618568755</v>
+        <v>0.06362550691112487</v>
       </c>
       <c r="AC10">
-        <v>-0.03590973618568755</v>
+        <v>-0.06362550691112487</v>
       </c>
       <c r="AD10">
-        <v>23168.7</v>
+        <v>5115.6</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>23168.7</v>
+        <v>5115.6</v>
       </c>
       <c r="AG10">
-        <v>20045.2</v>
+        <v>4520.200000000001</v>
       </c>
       <c r="AH10">
-        <v>0.8730814306224964</v>
+        <v>0.929281185852604</v>
       </c>
       <c r="AI10">
-        <v>0.8214860619641603</v>
+        <v>0.8235426694785646</v>
       </c>
       <c r="AJ10">
-        <v>0.8561495224915859</v>
+        <v>0.920704756085141</v>
       </c>
       <c r="AK10">
-        <v>0.7992535855406122</v>
+        <v>0.8048359240069084</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1695,7 +1704,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kyobo Securities Co.,Ltd. (KOSE:A030610)</t>
+          <t>SK Securities Co., Ltd. (KOSE:A001510)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1704,10 +1713,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.202</v>
+        <v>0.242</v>
       </c>
       <c r="E11">
-        <v>0.133</v>
+        <v>-0.191</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1722,85 +1731,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>135.8</v>
+        <v>3.52</v>
       </c>
       <c r="L11">
-        <v>0.07691000736251911</v>
+        <v>0.004317429167177726</v>
       </c>
       <c r="M11">
-        <v>24.2316</v>
+        <v>17.239</v>
       </c>
       <c r="N11">
-        <v>0.0542215260684717</v>
+        <v>0.08521502718734553</v>
       </c>
       <c r="O11">
-        <v>0.1784359351988218</v>
+        <v>4.897443181818182</v>
       </c>
       <c r="P11">
-        <v>24.2316</v>
+        <v>4.139</v>
       </c>
       <c r="Q11">
-        <v>0.0542215260684717</v>
+        <v>0.02045971329708354</v>
       </c>
       <c r="R11">
-        <v>0.1784359351988218</v>
+        <v>1.175852272727273</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.7599048668716283</v>
       </c>
       <c r="U11">
-        <v>104.5</v>
+        <v>169.1</v>
       </c>
       <c r="V11">
-        <v>0.2338330722756769</v>
+        <v>0.8358872960949085</v>
       </c>
       <c r="W11">
-        <v>0.1284039334341907</v>
+        <v>0.006676783004552352</v>
       </c>
       <c r="X11">
-        <v>0.1460166882518454</v>
+        <v>0.370036487632352</v>
       </c>
       <c r="Y11">
-        <v>-0.01761275481765473</v>
+        <v>-0.3633597046277996</v>
       </c>
       <c r="Z11">
-        <v>0.5680414361086089</v>
+        <v>0.2318669942893545</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03591229724010231</v>
+        <v>0.06363116845079056</v>
       </c>
       <c r="AC11">
-        <v>-0.03591229724010231</v>
+        <v>-0.06363116845079056</v>
       </c>
       <c r="AD11">
-        <v>3229.5</v>
+        <v>2623.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>3229.5</v>
+        <v>2623.6</v>
       </c>
       <c r="AG11">
-        <v>3125</v>
+        <v>2454.5</v>
       </c>
       <c r="AH11">
-        <v>0.8784408660646285</v>
+        <v>0.9284121872677731</v>
       </c>
       <c r="AI11">
-        <v>0.73439454235361</v>
+        <v>0.8515140696504495</v>
       </c>
       <c r="AJ11">
-        <v>0.8748845152439878</v>
+        <v>0.9238557663354411</v>
       </c>
       <c r="AK11">
-        <v>0.7279291870486839</v>
+        <v>0.8428914835164835</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1817,7 +1826,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Meritz Securities Co., Ltd. (KOSE:A008560)</t>
+          <t>Daishin Securities Co., Ltd. (KOSE:A003540)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1826,10 +1835,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.427</v>
+        <v>0.0379</v>
       </c>
       <c r="E12">
-        <v>0.234</v>
+        <v>0.148</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1844,85 +1853,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>616.7</v>
+        <v>155.6</v>
       </c>
       <c r="L12">
-        <v>0.0416708898393843</v>
+        <v>0.05754863525408684</v>
       </c>
       <c r="M12">
-        <v>326.2225</v>
+        <v>84.5</v>
       </c>
       <c r="N12">
-        <v>0.1262177899868452</v>
+        <v>0.1332597382116385</v>
       </c>
       <c r="O12">
-        <v>0.5289808658991406</v>
+        <v>0.5430591259640103</v>
       </c>
       <c r="P12">
-        <v>161.9225</v>
+        <v>65.7</v>
       </c>
       <c r="Q12">
-        <v>0.06264895921999536</v>
+        <v>0.1036114177574515</v>
       </c>
       <c r="R12">
-        <v>0.2625628344413816</v>
+        <v>0.4222365038560412</v>
       </c>
       <c r="S12">
-        <v>164.3</v>
+        <v>18.8</v>
       </c>
       <c r="T12">
-        <v>0.50364398531677</v>
+        <v>0.2224852071005917</v>
       </c>
       <c r="U12">
-        <v>820.6</v>
+        <v>603.4</v>
       </c>
       <c r="V12">
-        <v>0.3174959374758183</v>
+        <v>0.9515849235136413</v>
       </c>
       <c r="W12">
-        <v>0.164611360239163</v>
+        <v>0.07139907309686595</v>
       </c>
       <c r="X12">
-        <v>0.1717118173767858</v>
+        <v>0.3518273611473617</v>
       </c>
       <c r="Y12">
-        <v>-0.007100457137622834</v>
+        <v>-0.2804282880504957</v>
       </c>
       <c r="Z12">
-        <v>0.6350131943103557</v>
+        <v>0.2035472845807549</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.03592214837578204</v>
+        <v>0.06365898519778984</v>
       </c>
       <c r="AC12">
-        <v>-0.03592214837578204</v>
+        <v>-0.06365898519778984</v>
       </c>
       <c r="AD12">
-        <v>23019.7</v>
+        <v>7725</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>23019.7</v>
+        <v>7725</v>
       </c>
       <c r="AG12">
-        <v>22199.1</v>
+        <v>7121.6</v>
       </c>
       <c r="AH12">
-        <v>0.8990560179344876</v>
+        <v>0.9241425512315918</v>
       </c>
       <c r="AI12">
-        <v>0.8427031281459924</v>
+        <v>0.7966463508956471</v>
       </c>
       <c r="AJ12">
-        <v>0.8957137150627228</v>
+        <v>0.9182407777505576</v>
       </c>
       <c r="AK12">
-        <v>0.8378315135549274</v>
+        <v>0.7831528014515864</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1948,10 +1957,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.08599999999999999</v>
+        <v>0.0828</v>
       </c>
       <c r="E13">
-        <v>0.315</v>
+        <v>-0.0851</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1966,85 +1975,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>128.8</v>
+        <v>29.5</v>
       </c>
       <c r="L13">
-        <v>0.06922498118886382</v>
+        <v>0.01632449781417741</v>
       </c>
       <c r="M13">
-        <v>39.04</v>
+        <v>29.7</v>
       </c>
       <c r="N13">
-        <v>0.09632371083148285</v>
+        <v>0.08139216223622912</v>
       </c>
       <c r="O13">
-        <v>0.3031055900621117</v>
+        <v>1.006779661016949</v>
       </c>
       <c r="P13">
-        <v>30.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q13">
-        <v>0.07549962990377498</v>
+        <v>0.06522334886270212</v>
       </c>
       <c r="R13">
-        <v>0.2375776397515528</v>
+        <v>0.8067796610169492</v>
       </c>
       <c r="S13">
-        <v>8.439999999999998</v>
+        <v>5.900000000000002</v>
       </c>
       <c r="T13">
-        <v>0.2161885245901639</v>
+        <v>0.1986531986531987</v>
       </c>
       <c r="U13">
-        <v>284.4</v>
+        <v>110.1</v>
       </c>
       <c r="V13">
-        <v>0.7017024426350851</v>
+        <v>0.3017265004110715</v>
       </c>
       <c r="W13">
-        <v>0.123194643711143</v>
+        <v>0.02568567696996082</v>
       </c>
       <c r="X13">
-        <v>0.195164800329616</v>
+        <v>0.2942458375919358</v>
       </c>
       <c r="Y13">
-        <v>-0.07197015661847303</v>
+        <v>-0.268560160621975</v>
       </c>
       <c r="Z13">
-        <v>0.3682169008509796</v>
+        <v>0.3546532166267614</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.03592861418609657</v>
+        <v>0.06377386018374342</v>
       </c>
       <c r="AC13">
-        <v>-0.03592861418609657</v>
+        <v>-0.06377386018374342</v>
       </c>
       <c r="AD13">
-        <v>4231.3</v>
+        <v>3538.2</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>4231.3</v>
+        <v>3538.2</v>
       </c>
       <c r="AG13">
-        <v>3946.9</v>
+        <v>3428.1</v>
       </c>
       <c r="AH13">
-        <v>0.912586809299918</v>
+        <v>0.9065102098332095</v>
       </c>
       <c r="AI13">
-        <v>0.7784278013871258</v>
+        <v>0.7785332365172618</v>
       </c>
       <c r="AJ13">
-        <v>0.9068746840678278</v>
+        <v>0.9037964671763775</v>
       </c>
       <c r="AK13">
-        <v>0.7661949410828335</v>
+        <v>0.7730347720200242</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2061,7 +2070,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hyundai Motor Securities Co., Ltd. (KOSE:A001500)</t>
+          <t>Hanyang Securities Co. Ltd. (KOSE:A001750)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2070,10 +2079,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.117</v>
+        <v>0.46</v>
       </c>
       <c r="E14">
-        <v>0.145</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2088,85 +2097,82 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>78.7</v>
+        <v>26.3</v>
       </c>
       <c r="L14">
-        <v>0.1181681681681682</v>
+        <v>0.03539703903095558</v>
       </c>
       <c r="M14">
-        <v>18.1007</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.05501732522796352</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.2299961880559085</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>18.1007</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.05501732522796352</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.2299961880559085</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>488.9</v>
+        <v>132</v>
       </c>
       <c r="V14">
-        <v>1.486018237082067</v>
+        <v>1.596130592503023</v>
       </c>
       <c r="W14">
-        <v>0.08944198204341403</v>
+        <v>0.0745042492917847</v>
       </c>
       <c r="X14">
-        <v>0.2417530133073456</v>
+        <v>0.2832152077262263</v>
       </c>
       <c r="Y14">
-        <v>-0.1523110312639315</v>
+        <v>-0.2087109584344416</v>
       </c>
       <c r="Z14">
-        <v>0.1231804982706642</v>
+        <v>0.7887306001995712</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.03593739776412075</v>
+        <v>0.06380224528320233</v>
       </c>
       <c r="AC14">
-        <v>-0.03593739776412075</v>
+        <v>-0.06380224528320233</v>
       </c>
       <c r="AD14">
-        <v>4436.9</v>
+        <v>762.5</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>4436.9</v>
+        <v>762.5</v>
       </c>
       <c r="AG14">
-        <v>3948</v>
+        <v>630.5</v>
       </c>
       <c r="AH14">
-        <v>0.9309679179168677</v>
+        <v>0.902153336488405</v>
       </c>
       <c r="AI14">
-        <v>0.820250684019818</v>
+        <v>0.6961563042088925</v>
       </c>
       <c r="AJ14">
-        <v>0.923076923076923</v>
+        <v>0.8840437464946719</v>
       </c>
       <c r="AK14">
-        <v>0.802390098164746</v>
+        <v>0.6545209176788125</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2183,7 +2189,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DB Financial Investment Co., Ltd. (KOSE:A016610)</t>
+          <t>Samsung Securities Co., Ltd. (KOSE:A016360)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2192,7 +2198,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0406</v>
+        <v>0.26</v>
+      </c>
+      <c r="E15">
+        <v>0.187</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2207,28 +2216,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>120.1</v>
+        <v>387</v>
       </c>
       <c r="L15">
-        <v>0.1120335820895522</v>
+        <v>0.04674534056456776</v>
       </c>
       <c r="M15">
-        <v>10.5156</v>
+        <v>236.645</v>
       </c>
       <c r="N15">
-        <v>0.04591965065502183</v>
+        <v>0.1065248705829394</v>
       </c>
       <c r="O15">
-        <v>0.08755703580349708</v>
+        <v>0.611485788113695</v>
       </c>
       <c r="P15">
-        <v>10.5156</v>
+        <v>236.645</v>
       </c>
       <c r="Q15">
-        <v>0.04591965065502183</v>
+        <v>0.1065248705829394</v>
       </c>
       <c r="R15">
-        <v>0.08755703580349708</v>
+        <v>0.611485788113695</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2237,55 +2246,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>353.7</v>
+        <v>2002.1</v>
       </c>
       <c r="V15">
-        <v>1.544541484716157</v>
+        <v>0.9012379023182534</v>
       </c>
       <c r="W15">
-        <v>0.1859708888200681</v>
+        <v>0.07686654616958309</v>
       </c>
       <c r="X15">
-        <v>0.2491799329234713</v>
+        <v>0.2664680706680885</v>
       </c>
       <c r="Y15">
-        <v>-0.06320904410340317</v>
+        <v>-0.1896015244985054</v>
       </c>
       <c r="Z15">
-        <v>0.3136520568786939</v>
+        <v>0.3301009972129075</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03593846770182062</v>
+        <v>0.06385078327677778</v>
       </c>
       <c r="AC15">
-        <v>-0.03593846770182062</v>
+        <v>-0.06385078327677778</v>
       </c>
       <c r="AD15">
-        <v>3199.5</v>
+        <v>18876</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>3199.5</v>
+        <v>18876</v>
       </c>
       <c r="AG15">
-        <v>2845.8</v>
+        <v>16873.9</v>
       </c>
       <c r="AH15">
-        <v>0.9332069418112877</v>
+        <v>0.8947031638819766</v>
       </c>
       <c r="AI15">
-        <v>0.7867171555730409</v>
+        <v>0.8142524372357863</v>
       </c>
       <c r="AJ15">
-        <v>0.9255236112917914</v>
+        <v>0.8836630811609079</v>
       </c>
       <c r="AK15">
-        <v>0.7664009479694064</v>
+        <v>0.7966940353826033</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2302,7 +2311,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Daishin Securities Co., Ltd. (KOSE:A003540)</t>
+          <t>EBEST Investment &amp; Securities Co., Ltd. (KOSDAQ:A078020)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2311,10 +2320,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.00239</v>
+        <v>0.164</v>
       </c>
       <c r="E16">
-        <v>0.508</v>
+        <v>0.151</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2329,85 +2338,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>538.6</v>
+        <v>50.6</v>
       </c>
       <c r="L16">
-        <v>0.2007155101736603</v>
+        <v>0.0573826264459061</v>
       </c>
       <c r="M16">
-        <v>100.6</v>
+        <v>21.0672</v>
       </c>
       <c r="N16">
-        <v>0.1044001660440017</v>
+        <v>0.1056529588766299</v>
       </c>
       <c r="O16">
-        <v>0.1867805421463052</v>
+        <v>0.4163478260869565</v>
       </c>
       <c r="P16">
-        <v>68.09999999999999</v>
+        <v>21.0672</v>
       </c>
       <c r="Q16">
-        <v>0.07067247820672477</v>
+        <v>0.1056529588766299</v>
       </c>
       <c r="R16">
-        <v>0.1264389157073895</v>
+        <v>0.4163478260869565</v>
       </c>
       <c r="S16">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>0.3230616302186879</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3608.7</v>
+        <v>31.1</v>
       </c>
       <c r="V16">
-        <v>3.745018679950186</v>
+        <v>0.1559679037111334</v>
       </c>
       <c r="W16">
-        <v>0.3072973127175215</v>
+        <v>0.07349310094408133</v>
       </c>
       <c r="X16">
-        <v>0.2701160974440324</v>
+        <v>0.2491046792137188</v>
       </c>
       <c r="Y16">
-        <v>0.03718121527348911</v>
+        <v>-0.1756115782696375</v>
       </c>
       <c r="Z16">
-        <v>0.2682729317670582</v>
+        <v>0.3568162505563873</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.03594114151300559</v>
+        <v>0.06390958074855954</v>
       </c>
       <c r="AC16">
-        <v>-0.03594114151300559</v>
+        <v>-0.06390958074855954</v>
       </c>
       <c r="AD16">
-        <v>14782.1</v>
+        <v>1544.8</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>14782.1</v>
+        <v>1544.8</v>
       </c>
       <c r="AG16">
-        <v>11173.4</v>
+        <v>1513.7</v>
       </c>
       <c r="AH16">
-        <v>0.9388023396863906</v>
+        <v>0.8856782479073501</v>
       </c>
       <c r="AI16">
-        <v>0.8701392731425343</v>
+        <v>0.7036210430425871</v>
       </c>
       <c r="AJ16">
-        <v>0.9206064101507786</v>
+        <v>0.8836028252874905</v>
       </c>
       <c r="AK16">
-        <v>0.8351134197839979</v>
+        <v>0.6993624099057475</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2424,7 +2433,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Woori Investment Bank Co., Ltd. (KOSE:A010050)</t>
+          <t>Kiwoom Securities Co., Ltd. (KOSE:A039490)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2433,10 +2442,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.241</v>
+        <v>0.505</v>
       </c>
       <c r="E17">
-        <v>0.347</v>
+        <v>0.213</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2451,85 +2460,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>67.09999999999999</v>
+        <v>390.7</v>
       </c>
       <c r="L17">
-        <v>0.3330024813895781</v>
+        <v>0.07319769184652278</v>
       </c>
       <c r="M17">
-        <v>6.9928</v>
+        <v>132.2</v>
       </c>
       <c r="N17">
-        <v>0.01055835723992149</v>
+        <v>0.07197299651567944</v>
       </c>
       <c r="O17">
-        <v>0.1042146050670641</v>
+        <v>0.3383670335295623</v>
       </c>
       <c r="P17">
-        <v>6.9928</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Q17">
-        <v>0.01055835723992149</v>
+        <v>0.04006968641114982</v>
       </c>
       <c r="R17">
-        <v>0.1042146050670641</v>
+        <v>0.1883798310724341</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>58.59999999999999</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.443267776096823</v>
       </c>
       <c r="U17">
-        <v>220.2</v>
+        <v>1014.6</v>
       </c>
       <c r="V17">
-        <v>0.3324777291257738</v>
+        <v>0.5523736933797909</v>
       </c>
       <c r="W17">
-        <v>0.1871687587168759</v>
+        <v>0.1137839648192912</v>
       </c>
       <c r="X17">
-        <v>0.04985166071546367</v>
+        <v>0.2128489156687165</v>
       </c>
       <c r="Y17">
-        <v>0.1373170980014122</v>
+        <v>-0.09906495084942532</v>
       </c>
       <c r="Z17">
-        <v>0.3429203539823009</v>
+        <v>0.4065318059956131</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.0374009871853573</v>
+        <v>0.06407193120673169</v>
       </c>
       <c r="AC17">
-        <v>-0.0374009871853573</v>
+        <v>-0.06407193120673169</v>
       </c>
       <c r="AD17">
-        <v>621.8</v>
+        <v>11354.7</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>621.8</v>
+        <v>11354.7</v>
       </c>
       <c r="AG17">
-        <v>401.6</v>
+        <v>10340.1</v>
       </c>
       <c r="AH17">
-        <v>0.484230200140176</v>
+        <v>0.860758821968692</v>
       </c>
       <c r="AI17">
-        <v>0.55612199266613</v>
+        <v>0.7850372306224462</v>
       </c>
       <c r="AJ17">
-        <v>0.3774790863802989</v>
+        <v>0.8491570104049472</v>
       </c>
       <c r="AK17">
-        <v>0.4472658425214389</v>
+        <v>0.7688206821172849</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2546,7 +2555,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Korea Asset Investment Securities Co., Ltd. (KOSDAQ:A190650)</t>
+          <t>BOOKOOK Securities Co., Ltd. (KOSE:A001270)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2554,6 +2563,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="E18">
+        <v>0.0475</v>
+      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2567,82 +2582,85 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>12</v>
+        <v>31.2</v>
       </c>
       <c r="L18">
-        <v>0.082930200414651</v>
+        <v>0.04904118201823326</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.0782472613458529</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0.3205128205128205</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.0782472613458529</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.3205128205128205</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>28.3</v>
+        <v>204.5</v>
       </c>
       <c r="V18">
-        <v>0.466996699669967</v>
+        <v>1.600156494522692</v>
       </c>
       <c r="W18">
-        <v>0.1857585139318886</v>
+        <v>0.05653198043123754</v>
       </c>
       <c r="X18">
-        <v>0.05300788937318119</v>
+        <v>0.2055399857378887</v>
       </c>
       <c r="Y18">
-        <v>0.1327506245587074</v>
+        <v>-0.1490080053066511</v>
       </c>
       <c r="Z18">
-        <v>0.8029966703662597</v>
+        <v>0.867466593946005</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.03759653488817664</v>
+        <v>0.06411362631617069</v>
       </c>
       <c r="AC18">
-        <v>-0.03759653488817664</v>
+        <v>-0.06411362631617069</v>
       </c>
       <c r="AD18">
-        <v>69.40000000000001</v>
+        <v>749.7</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>69.40000000000001</v>
+        <v>749.7</v>
       </c>
       <c r="AG18">
-        <v>41.10000000000001</v>
+        <v>545.2</v>
       </c>
       <c r="AH18">
-        <v>0.5338461538461539</v>
+        <v>0.8543589743589745</v>
       </c>
       <c r="AI18">
-        <v>0.4829505915100906</v>
+        <v>0.6026042922594648</v>
       </c>
       <c r="AJ18">
-        <v>0.4041297935103245</v>
+        <v>0.8101040118870729</v>
       </c>
       <c r="AK18">
-        <v>0.3561525129982669</v>
+        <v>0.5244324740284726</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2659,7 +2677,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hanwha Investment &amp; Securities Co., Ltd. (KOSE:A003530)</t>
+          <t>Sangsangin Investment &amp; Securities Co.,Ltd. (KOSE:A001290)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2668,7 +2686,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0701</v>
+        <v>0.00078</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2683,10 +2701,10 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>110.5</v>
+        <v>0.923</v>
       </c>
       <c r="L19">
-        <v>0.06329476457784397</v>
+        <v>0.03238596491228071</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2710,55 +2728,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>155.4</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
-        <v>0.1327637761640325</v>
+        <v>0.03442879499217528</v>
       </c>
       <c r="W19">
-        <v>0.1079523251270027</v>
+        <v>0.005655637254901961</v>
       </c>
       <c r="X19">
-        <v>0.1079086436847538</v>
+        <v>0.1200587866589167</v>
       </c>
       <c r="Y19">
-        <v>4.368144224894954e-05</v>
+        <v>-0.1144031494040148</v>
       </c>
       <c r="Z19">
-        <v>0.3311833668475169</v>
+        <v>0.07293666026871401</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.03874650700853312</v>
+        <v>0.06521656926212221</v>
       </c>
       <c r="AC19">
-        <v>-0.03874650700853312</v>
+        <v>-0.06521656926212221</v>
       </c>
       <c r="AD19">
-        <v>5542.1</v>
+        <v>139</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>5542.1</v>
+        <v>139</v>
       </c>
       <c r="AG19">
-        <v>5386.700000000001</v>
+        <v>136.8</v>
       </c>
       <c r="AH19">
-        <v>0.8256264338706314</v>
+        <v>0.6850665352390339</v>
       </c>
       <c r="AI19">
-        <v>0.8044854115256206</v>
+        <v>0.4548429319371727</v>
       </c>
       <c r="AJ19">
-        <v>0.8214939303361191</v>
+        <v>0.6816143497757847</v>
       </c>
       <c r="AK19">
-        <v>0.7999732683854105</v>
+        <v>0.4508899143045485</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2775,7 +2793,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kiwoom Securities Co., Ltd. (KOSE:A039490)</t>
+          <t>Yuhwa Securities co.,ltd. (KOSE:A003460)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2784,10 +2802,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.357</v>
+        <v>0.013</v>
       </c>
       <c r="E20">
-        <v>0.424</v>
+        <v>-0.0495</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2802,85 +2820,82 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>783.6</v>
+        <v>4.48</v>
       </c>
       <c r="L20">
-        <v>0.271433025044165</v>
+        <v>0.3419847328244275</v>
       </c>
       <c r="M20">
-        <v>65.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.02829086819223948</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>0.08346094946401225</v>
+        <v>-0</v>
       </c>
       <c r="P20">
-        <v>65.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.02829086819223948</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.08346094946401225</v>
+        <v>-0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
-        <v>1273.2</v>
+        <v>14.5</v>
       </c>
       <c r="V20">
-        <v>0.5507635073755246</v>
+        <v>0.1757575757575758</v>
       </c>
       <c r="W20">
-        <v>0.3486695737296431</v>
+        <v>0.01133029843196763</v>
       </c>
       <c r="X20">
-        <v>0.1080649820495876</v>
+        <v>0.09618026188511215</v>
       </c>
       <c r="Y20">
-        <v>0.2406045916800556</v>
+        <v>-0.08484996345314452</v>
       </c>
       <c r="Z20">
-        <v>0.2590913986214819</v>
+        <v>0.02482758097866155</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.03874772980036754</v>
+        <v>0.06620314929400174</v>
       </c>
       <c r="AC20">
-        <v>-0.03874772980036754</v>
+        <v>-0.06620314929400174</v>
       </c>
       <c r="AD20">
-        <v>10969.1</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>10969.1</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AG20">
-        <v>9695.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AH20">
-        <v>0.8259366905608096</v>
+        <v>0.5336348219332957</v>
       </c>
       <c r="AI20">
-        <v>0.75998032341652</v>
+        <v>0.2061135371179039</v>
       </c>
       <c r="AJ20">
-        <v>0.8074802625004165</v>
+        <v>0.4919950738916256</v>
       </c>
       <c r="AK20">
-        <v>0.7367593197671767</v>
+        <v>0.1801578354002255</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2897,7 +2912,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NH Investment &amp; Securities Co., Ltd. (KOSE:A005940)</t>
+          <t>Daol Investment &amp; Securities Co., Ltd. (KOSE:A030210)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2906,10 +2921,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.0498</v>
+        <v>0.402</v>
       </c>
       <c r="E21">
-        <v>0.342</v>
+        <v>0.311</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2924,85 +2939,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>692.2</v>
+        <v>97.3</v>
       </c>
       <c r="L21">
-        <v>0.08484298776750913</v>
+        <v>0.08939728041161336</v>
       </c>
       <c r="M21">
-        <v>178.2</v>
+        <v>12.2764</v>
       </c>
       <c r="N21">
-        <v>0.05384011118496585</v>
+        <v>0.09465227447956824</v>
       </c>
       <c r="O21">
-        <v>0.2574400462294134</v>
+        <v>0.1261706063720452</v>
       </c>
       <c r="P21">
-        <v>178.2</v>
+        <v>10.1964</v>
       </c>
       <c r="Q21">
-        <v>0.05384011118496585</v>
+        <v>0.07861526599845797</v>
       </c>
       <c r="R21">
-        <v>0.2574400462294134</v>
+        <v>0.1047934224049332</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>0.1694307777524356</v>
       </c>
       <c r="U21">
-        <v>2018</v>
+        <v>168.4</v>
       </c>
       <c r="V21">
-        <v>0.6097045138679074</v>
+        <v>1.298380878951427</v>
       </c>
       <c r="W21">
-        <v>0.1397423991601728</v>
+        <v>0.1727627840909091</v>
       </c>
       <c r="X21">
-        <v>0.1274441948418983</v>
+        <v>0.5302338614202502</v>
       </c>
       <c r="Y21">
-        <v>0.01229820431827455</v>
+        <v>-0.3574710773293411</v>
       </c>
       <c r="Z21">
-        <v>0.315853861550195</v>
+        <v>0.4194866260695291</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.03887169317302175</v>
+        <v>0.06897520408959962</v>
       </c>
       <c r="AC21">
-        <v>-0.03887169317302175</v>
+        <v>-0.06897520408959962</v>
       </c>
       <c r="AD21">
-        <v>19898.9</v>
+        <v>2579.2</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>19898.9</v>
+        <v>2579.2</v>
       </c>
       <c r="AG21">
-        <v>17880.9</v>
+        <v>2410.8</v>
       </c>
       <c r="AH21">
-        <v>0.8573896857643901</v>
+        <v>0.9521207870353281</v>
       </c>
       <c r="AI21">
-        <v>0.7849478907797054</v>
+        <v>0.7846429983876365</v>
       </c>
       <c r="AJ21">
-        <v>0.8438088406706716</v>
+        <v>0.9489470576658139</v>
       </c>
       <c r="AK21">
-        <v>0.7663483709488013</v>
+        <v>0.7730143970244011</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3019,7 +3034,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yuanta Securities Korea Co., Ltd. (KOSE:A003470)</t>
+          <t>Hanwha Investment &amp; Securities Co., Ltd. (KOSE:A003530)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3028,10 +3043,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.136</v>
+        <v>0.0527</v>
       </c>
       <c r="E22">
-        <v>0.535</v>
+        <v>0.269</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3046,28 +3061,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>203.9</v>
+        <v>39.3</v>
       </c>
       <c r="L22">
-        <v>0.1097475644544916</v>
+        <v>0.03026336054212228</v>
       </c>
       <c r="M22">
-        <v>22.3</v>
+        <v>30.3159</v>
       </c>
       <c r="N22">
-        <v>0.03213719556132007</v>
+        <v>0.07478021706956094</v>
       </c>
       <c r="O22">
-        <v>0.1093673369298676</v>
+        <v>0.7713969465648857</v>
       </c>
       <c r="P22">
-        <v>22.3</v>
+        <v>30.3159</v>
       </c>
       <c r="Q22">
-        <v>0.03213719556132007</v>
+        <v>0.07478021706956094</v>
       </c>
       <c r="R22">
-        <v>0.1093673369298676</v>
+        <v>0.7713969465648857</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3076,55 +3091,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>671.6</v>
+        <v>179</v>
       </c>
       <c r="V22">
-        <v>0.96786280443868</v>
+        <v>0.4415392205229403</v>
       </c>
       <c r="W22">
-        <v>0.1777680906713165</v>
+        <v>0.02963577407435337</v>
       </c>
       <c r="X22">
-        <v>0.1558198934081719</v>
+        <v>0.3784586327527228</v>
       </c>
       <c r="Y22">
-        <v>0.02194819726314456</v>
+        <v>-0.3488228586783695</v>
       </c>
       <c r="Z22">
-        <v>0.2946148235070248</v>
+        <v>0.1933418693982074</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.03898929105281505</v>
+        <v>0.06899140469060373</v>
       </c>
       <c r="AC22">
-        <v>-0.03898929105281505</v>
+        <v>-0.06899140469060373</v>
       </c>
       <c r="AD22">
-        <v>5459.2</v>
+        <v>5405</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>5459.2</v>
+        <v>5405</v>
       </c>
       <c r="AG22">
-        <v>4787.599999999999</v>
+        <v>5226</v>
       </c>
       <c r="AH22">
-        <v>0.8872275763436317</v>
+        <v>0.9302285556932398</v>
       </c>
       <c r="AI22">
-        <v>0.8040414156737411</v>
+        <v>0.8241465013799307</v>
       </c>
       <c r="AJ22">
-        <v>0.8734105628021528</v>
+        <v>0.9280107966047519</v>
       </c>
       <c r="AK22">
-        <v>0.7825305241823441</v>
+        <v>0.8192121392629285</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3141,7 +3156,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Korea Investment Holdings Co., Ltd. (KOSE:A071050)</t>
+          <t>Meritz Securities Co., Ltd. (KOSE:A008560)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3150,10 +3165,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.321</v>
+        <v>0.61</v>
       </c>
       <c r="E23">
-        <v>0.522</v>
+        <v>0.211</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3168,85 +3183,85 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>1522.6</v>
+        <v>586.4</v>
       </c>
       <c r="L23">
-        <v>0.1106291460499451</v>
+        <v>0.01776786634104365</v>
       </c>
       <c r="M23">
-        <v>148</v>
+        <v>205.812</v>
       </c>
       <c r="N23">
-        <v>0.03738695498408529</v>
+        <v>0.07844042991081637</v>
       </c>
       <c r="O23">
-        <v>0.09720215420990412</v>
+        <v>0.3509754433833561</v>
       </c>
       <c r="P23">
-        <v>148</v>
+        <v>37.212</v>
       </c>
       <c r="Q23">
-        <v>0.03738695498408529</v>
+        <v>0.01418248342099245</v>
       </c>
       <c r="R23">
-        <v>0.09720215420990412</v>
+        <v>0.06345839017735334</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>168.6</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>0.8191942160806951</v>
       </c>
       <c r="U23">
-        <v>12108.8</v>
+        <v>669.3</v>
       </c>
       <c r="V23">
-        <v>3.058859192643864</v>
+        <v>0.25508804024697</v>
       </c>
       <c r="W23">
-        <v>0.3329834229978568</v>
+        <v>0.1426208775172682</v>
       </c>
       <c r="X23">
-        <v>0.1659952165001994</v>
+        <v>0.2397031072437286</v>
       </c>
       <c r="Y23">
-        <v>0.1669882064976573</v>
+        <v>-0.09708222972646038</v>
       </c>
       <c r="Z23">
-        <v>0.6158703025855355</v>
+        <v>1.250574068039378</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.03902031047161687</v>
+        <v>0.06902848982277364</v>
       </c>
       <c r="AC23">
-        <v>-0.03902031047161687</v>
+        <v>-0.06902848982277364</v>
       </c>
       <c r="AD23">
-        <v>33777.6</v>
+        <v>19262.1</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>33777.6</v>
+        <v>19262.1</v>
       </c>
       <c r="AG23">
-        <v>21668.8</v>
+        <v>18592.8</v>
       </c>
       <c r="AH23">
-        <v>0.8950980755878971</v>
+        <v>0.880114594327855</v>
       </c>
       <c r="AI23">
-        <v>0.8490524775844777</v>
+        <v>0.8256683712616432</v>
       </c>
       <c r="AJ23">
-        <v>0.8455325159789913</v>
+        <v>0.8763326828992393</v>
       </c>
       <c r="AK23">
-        <v>0.7830049252183464</v>
+        <v>0.8205191572741154</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3263,7 +3278,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SK Securities Co., Ltd. (KOSE:A001510)</t>
+          <t>NH Investment &amp; Securities Co., Ltd. (KOSE:A005940)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3272,10 +3287,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.181</v>
+        <v>0.0915</v>
       </c>
       <c r="E24">
-        <v>0.3</v>
+        <v>0.0581</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3290,28 +3305,28 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>41.6</v>
+        <v>294.7</v>
       </c>
       <c r="L24">
-        <v>0.05098664051967153</v>
+        <v>0.03439582628181935</v>
       </c>
       <c r="M24">
-        <v>3.4632</v>
+        <v>231.1</v>
       </c>
       <c r="N24">
-        <v>0.009524752475247525</v>
+        <v>0.09522043675319324</v>
       </c>
       <c r="O24">
-        <v>0.08325</v>
+        <v>0.7841873091279267</v>
       </c>
       <c r="P24">
-        <v>3.4632</v>
+        <v>231.1</v>
       </c>
       <c r="Q24">
-        <v>0.009524752475247525</v>
+        <v>0.09522043675319324</v>
       </c>
       <c r="R24">
-        <v>0.08325</v>
+        <v>0.7841873091279267</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3320,55 +3335,55 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>239.4</v>
+        <v>1193.4</v>
       </c>
       <c r="V24">
-        <v>0.6584158415841584</v>
+        <v>0.4917181705809642</v>
       </c>
       <c r="W24">
-        <v>0.08627125673994193</v>
+        <v>0.05410118960199736</v>
       </c>
       <c r="X24">
-        <v>0.1713417490986953</v>
+        <v>0.2375013250579086</v>
       </c>
       <c r="Y24">
-        <v>-0.08507049235875336</v>
+        <v>-0.1834001354559113</v>
       </c>
       <c r="Z24">
-        <v>0.2615248511112963</v>
+        <v>0.3678094305927604</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.03903493551748272</v>
+        <v>0.06902951262283588</v>
       </c>
       <c r="AC24">
-        <v>-0.03903493551748272</v>
+        <v>-0.06902951262283588</v>
       </c>
       <c r="AD24">
-        <v>3229.6</v>
+        <v>17586.6</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>3229.6</v>
+        <v>17586.6</v>
       </c>
       <c r="AG24">
-        <v>2990.2</v>
+        <v>16393.2</v>
       </c>
       <c r="AH24">
-        <v>0.8988088611822331</v>
+        <v>0.8787324619258904</v>
       </c>
       <c r="AI24">
-        <v>0.8577271399357288</v>
+        <v>0.7754814073365287</v>
       </c>
       <c r="AJ24">
-        <v>0.8915856640228994</v>
+        <v>0.8710428156980266</v>
       </c>
       <c r="AK24">
-        <v>0.8480671601576902</v>
+        <v>0.76301030025739</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3385,7 +3400,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KTB Investment &amp; Securities Co., Ltd. (KOSE:A030210)</t>
+          <t>Woori Investment Bank Co.,Ltd. (KOSE:A010050)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3394,10 +3409,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.247</v>
+        <v>0.194</v>
       </c>
       <c r="E25">
-        <v>0.418</v>
+        <v>0.283</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3412,85 +3427,85 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>130.5</v>
+        <v>56.9</v>
       </c>
       <c r="L25">
-        <v>0.2247674819152601</v>
+        <v>0.3232954545454546</v>
       </c>
       <c r="M25">
-        <v>8.268000000000001</v>
+        <v>12.2374</v>
       </c>
       <c r="N25">
-        <v>0.03213369607462107</v>
+        <v>0.02378965785381027</v>
       </c>
       <c r="O25">
-        <v>0.06335632183908046</v>
+        <v>0.2150685413005273</v>
       </c>
       <c r="P25">
-        <v>7.493</v>
+        <v>12.2374</v>
       </c>
       <c r="Q25">
-        <v>0.02912164788184998</v>
+        <v>0.02378965785381027</v>
       </c>
       <c r="R25">
-        <v>0.0574176245210728</v>
+        <v>0.2150685413005273</v>
       </c>
       <c r="S25">
-        <v>0.7750000000000004</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>0.09373488147073056</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>304.9</v>
+        <v>215.8</v>
       </c>
       <c r="V25">
-        <v>1.184998056743101</v>
+        <v>0.4195178849144635</v>
       </c>
       <c r="W25">
-        <v>0.312126285577613</v>
+        <v>0.1146483981462825</v>
       </c>
       <c r="X25">
-        <v>0.1717808604293595</v>
+        <v>0.09648199252215534</v>
       </c>
       <c r="Y25">
-        <v>0.1403454251482535</v>
+        <v>0.01816640562412715</v>
       </c>
       <c r="Z25">
-        <v>0.3077330789208671</v>
+        <v>0.1960129190333</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.03903609082814351</v>
+        <v>0.06928280615696812</v>
       </c>
       <c r="AC25">
-        <v>-0.03903609082814351</v>
+        <v>-0.06928280615696812</v>
       </c>
       <c r="AD25">
-        <v>2292.8</v>
+        <v>595.3</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>2292.8</v>
+        <v>595.3</v>
       </c>
       <c r="AG25">
-        <v>1987.9</v>
+        <v>379.4999999999999</v>
       </c>
       <c r="AH25">
-        <v>0.8991019960001568</v>
+        <v>0.5364512931422908</v>
       </c>
       <c r="AI25">
-        <v>0.7727410602945637</v>
+        <v>0.5678176268599771</v>
       </c>
       <c r="AJ25">
-        <v>0.8853999643684304</v>
+        <v>0.4245441324532945</v>
       </c>
       <c r="AK25">
-        <v>0.7467132446848472</v>
+        <v>0.4558011049723757</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3507,7 +3522,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Eugene Investment &amp; Securities Co.,Ltd. (KOSE:A001200)</t>
+          <t>Korea Asset Investment Securities Co., Ltd. (KOSDAQ:A190650)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3515,12 +3530,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D26">
-        <v>0.168</v>
-      </c>
-      <c r="E26">
-        <v>0.192</v>
-      </c>
       <c r="G26">
         <v>0</v>
       </c>
@@ -3534,85 +3543,82 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>77.90000000000001</v>
+        <v>4.52</v>
       </c>
       <c r="L26">
-        <v>0.07183033656062703</v>
+        <v>0.02676139727649497</v>
       </c>
       <c r="M26">
-        <v>9.567599999999999</v>
+        <v>-0</v>
       </c>
       <c r="N26">
-        <v>0.03376005645730416</v>
+        <v>-0</v>
       </c>
       <c r="O26">
-        <v>0.1228189987163029</v>
+        <v>-0</v>
       </c>
       <c r="P26">
-        <v>9.567599999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.03376005645730416</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>0.1228189987163029</v>
+        <v>-0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
-        <v>388</v>
+        <v>17.2</v>
       </c>
       <c r="V26">
-        <v>1.36908962597036</v>
+        <v>0.4586666666666667</v>
       </c>
       <c r="W26">
-        <v>0.1074630983583943</v>
+        <v>0.06083445491251682</v>
       </c>
       <c r="X26">
-        <v>0.2310977976565948</v>
+        <v>0.08351393401693084</v>
       </c>
       <c r="Y26">
-        <v>-0.1236346992982005</v>
+        <v>-0.02267947910441402</v>
       </c>
       <c r="Z26">
-        <v>0.2697895417682472</v>
+        <v>1.463604852686309</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.0391479358802639</v>
+        <v>0.06940305483055931</v>
       </c>
       <c r="AC26">
-        <v>-0.0391479358802639</v>
+        <v>-0.06940305483055931</v>
       </c>
       <c r="AD26">
-        <v>3624.5</v>
+        <v>22.4</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>3624.5</v>
+        <v>22.4</v>
       </c>
       <c r="AG26">
-        <v>3236.5</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="AH26">
-        <v>0.9274802323498554</v>
+        <v>0.3739565943238731</v>
       </c>
       <c r="AI26">
-        <v>0.8188924787058584</v>
+        <v>0.2638398115429917</v>
       </c>
       <c r="AJ26">
-        <v>0.9194863490440069</v>
+        <v>0.1217798594847775</v>
       </c>
       <c r="AK26">
-        <v>0.8014908001287735</v>
+        <v>0.07680945347119644</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/research/traditional_assets/database/data/south_korea/south_korea_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AQ24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1885</v>
+        <v>0.1151</v>
       </c>
       <c r="E2">
-        <v>0.1495</v>
+        <v>0.04775</v>
       </c>
       <c r="G2">
-        <v>0.02234522985960075</v>
+        <v>0.02265030709415676</v>
       </c>
       <c r="H2">
-        <v>0.02231954889089072</v>
+        <v>0.02260593339719389</v>
       </c>
       <c r="I2">
-        <v>0.01300970004031315</v>
+        <v>0.03321688172648898</v>
       </c>
       <c r="J2">
-        <v>0.009591040104876226</v>
+        <v>0.02625506330745982</v>
       </c>
       <c r="K2">
-        <v>3209.013</v>
+        <v>2834.48</v>
       </c>
       <c r="L2">
-        <v>0.03194207846630866</v>
+        <v>0.04991125260607426</v>
       </c>
       <c r="M2">
-        <v>1398.0579</v>
+        <v>668.1727</v>
       </c>
       <c r="N2">
-        <v>0.08131694847231674</v>
+        <v>0.04339544595481026</v>
       </c>
       <c r="O2">
-        <v>0.4356660131947113</v>
+        <v>0.2357302574017104</v>
       </c>
       <c r="P2">
-        <v>1126.5679</v>
+        <v>647.4417</v>
       </c>
       <c r="Q2">
-        <v>0.06552594415071512</v>
+        <v>0.04204904106564138</v>
       </c>
       <c r="R2">
-        <v>0.3510636759651644</v>
+        <v>0.2284163938359064</v>
       </c>
       <c r="S2">
-        <v>271.49</v>
+        <v>20.731</v>
       </c>
       <c r="T2">
-        <v>0.1941908128411563</v>
+        <v>0.03102640978896623</v>
       </c>
       <c r="U2">
-        <v>18937.4</v>
+        <v>22855.6</v>
       </c>
       <c r="V2">
-        <v>1.1014791161365</v>
+        <v>1.484390120345775</v>
       </c>
       <c r="W2">
-        <v>0.06611676400469138</v>
+        <v>0.03893786807032906</v>
       </c>
       <c r="X2">
-        <v>0.3230365993696487</v>
+        <v>0.2484092848509585</v>
       </c>
       <c r="Y2">
-        <v>-0.2569198353649573</v>
+        <v>-0.2094714167806294</v>
       </c>
       <c r="Z2">
-        <v>0.4779129947889176</v>
+        <v>0.3319902214690643</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06382651427999006</v>
+        <v>0.05375851796582472</v>
       </c>
       <c r="AC2">
-        <v>-0.06382651427999006</v>
+        <v>-0.05374439160146592</v>
       </c>
       <c r="AD2">
-        <v>177761.9</v>
+        <v>179693.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>177761.9</v>
+        <v>179693.5</v>
       </c>
       <c r="AG2">
-        <v>158824.5</v>
+        <v>156837.9</v>
       </c>
       <c r="AH2">
-        <v>0.9118117756646932</v>
+        <v>0.9210762373212884</v>
       </c>
       <c r="AI2">
-        <v>0.811086340349654</v>
+        <v>0.8097292693697672</v>
       </c>
       <c r="AJ2">
-        <v>0.9023237501789597</v>
+        <v>0.9106030590727099</v>
       </c>
       <c r="AK2">
-        <v>0.7932190235321969</v>
+        <v>0.7878830959538315</v>
       </c>
       <c r="AL2">
-        <v>133.05</v>
+        <v>324.11</v>
       </c>
       <c r="AM2">
-        <v>130.416</v>
+        <v>318.78</v>
       </c>
       <c r="AN2">
-        <v>127.8678607394619</v>
+        <v>90.69016856767941</v>
       </c>
       <c r="AO2">
-        <v>9.823374671176248</v>
+        <v>5.820246212705564</v>
       </c>
       <c r="AP2">
-        <v>114.2457919723781</v>
+        <v>79.15509235893812</v>
       </c>
       <c r="AQ2">
-        <v>10.02177646914489</v>
+        <v>5.917560700169396</v>
       </c>
     </row>
     <row r="3">
@@ -721,41 +721,47 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.341</v>
+      </c>
+      <c r="E3">
+        <v>0.314</v>
+      </c>
       <c r="G3">
-        <v>0.1663635576340175</v>
+        <v>0.08958931552587646</v>
       </c>
       <c r="H3">
-        <v>0.1663635576340175</v>
+        <v>0.08958931552587646</v>
       </c>
       <c r="I3">
-        <v>0.1064057042233192</v>
+        <v>0.1478063439065108</v>
       </c>
       <c r="J3">
-        <v>0.07647008858732103</v>
+        <v>0.1329424122650671</v>
       </c>
       <c r="K3">
-        <v>64.40000000000001</v>
+        <v>183.7</v>
       </c>
       <c r="L3">
-        <v>0.009295343667907971</v>
+        <v>0.02453422370617696</v>
       </c>
       <c r="M3">
-        <v>8.0047</v>
+        <v>8.540899999999999</v>
       </c>
       <c r="N3">
-        <v>0.008537436006825938</v>
+        <v>0.02084163006344558</v>
       </c>
       <c r="O3">
-        <v>0.1242965838509317</v>
+        <v>0.04649373979314099</v>
       </c>
       <c r="P3">
-        <v>8.0047</v>
+        <v>8.540899999999999</v>
       </c>
       <c r="Q3">
-        <v>0.008537436006825938</v>
+        <v>0.02084163006344558</v>
       </c>
       <c r="R3">
-        <v>0.1242965838509317</v>
+        <v>0.04649373979314099</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1144.2</v>
+        <v>1300</v>
       </c>
       <c r="V3">
-        <v>1.220349829351536</v>
+        <v>3.17227916056613</v>
       </c>
       <c r="W3">
-        <v>0.08262766230433669</v>
+        <v>0.2578607523862998</v>
       </c>
       <c r="X3">
-        <v>0.4527162972115989</v>
+        <v>0.7946951095602071</v>
       </c>
       <c r="Y3">
-        <v>-0.3700886349072622</v>
+        <v>-0.5368343571739073</v>
       </c>
       <c r="Z3">
-        <v>0.3695375047337625</v>
+        <v>0.5027360929264445</v>
       </c>
       <c r="AA3">
-        <v>0.02825856572332838</v>
+        <v>0.06683494892635648</v>
       </c>
       <c r="AB3">
-        <v>0.06353623527060537</v>
+        <v>0.05766365665942035</v>
       </c>
       <c r="AC3">
-        <v>-0.03527766954727699</v>
+        <v>0.009171292266936137</v>
       </c>
       <c r="AD3">
-        <v>15506.8</v>
+        <v>19500</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15506.8</v>
+        <v>19500</v>
       </c>
       <c r="AG3">
-        <v>14362.6</v>
+        <v>18200</v>
       </c>
       <c r="AH3">
-        <v>0.9429836296854858</v>
+        <v>0.9794171714432089</v>
       </c>
       <c r="AI3">
-        <v>0.8117808419972568</v>
+        <v>0.8133879485104573</v>
       </c>
       <c r="AJ3">
-        <v>0.9387197552973163</v>
+        <v>0.9779793442164881</v>
       </c>
       <c r="AK3">
-        <v>0.7997883951442253</v>
+        <v>0.8026885656572784</v>
       </c>
       <c r="AL3">
-        <v>127.8</v>
+        <v>319.4</v>
       </c>
       <c r="AM3">
-        <v>126.12</v>
+        <v>315.81</v>
       </c>
       <c r="AN3">
-        <v>19.66370783667258</v>
+        <v>16.8335635359116</v>
       </c>
       <c r="AO3">
-        <v>5.768388106416276</v>
+        <v>3.464934251721979</v>
       </c>
       <c r="AP3">
-        <v>18.21278214557443</v>
+        <v>15.71132596685083</v>
       </c>
       <c r="AQ3">
-        <v>5.845226768157311</v>
+        <v>3.504322219055762</v>
       </c>
     </row>
     <row r="4">
@@ -850,121 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.489</v>
+        <v>0.37</v>
       </c>
       <c r="E4">
-        <v>0.223</v>
+        <v>0.24</v>
       </c>
       <c r="G4">
-        <v>0.1671021632041122</v>
+        <v>0.08627494954025566</v>
       </c>
       <c r="H4">
-        <v>0.166707462595233</v>
+        <v>0.0859217313298946</v>
       </c>
       <c r="I4">
-        <v>0.08717070036410365</v>
+        <v>0.1092873962771922</v>
       </c>
       <c r="J4">
-        <v>0.06525803807367775</v>
+        <v>0.09529805933396948</v>
       </c>
       <c r="K4">
-        <v>198.7</v>
+        <v>349.5</v>
       </c>
       <c r="L4">
-        <v>0.03039806627298595</v>
+        <v>0.04898800179412425</v>
       </c>
       <c r="M4">
-        <v>19.4776</v>
+        <v>19.2672</v>
       </c>
       <c r="N4">
-        <v>0.02972318022279872</v>
+        <v>0.03212270756918974</v>
       </c>
       <c r="O4">
-        <v>0.09802516356316056</v>
+        <v>0.05512789699570816</v>
       </c>
       <c r="P4">
-        <v>18.0576</v>
+        <v>19.2672</v>
       </c>
       <c r="Q4">
-        <v>0.02755623378605219</v>
+        <v>0.03212270756918974</v>
       </c>
       <c r="R4">
-        <v>0.09087871162556618</v>
+        <v>0.05512789699570816</v>
       </c>
       <c r="S4">
-        <v>1.420000000000002</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.07290425925165325</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1052.8</v>
+        <v>1232.1</v>
       </c>
       <c r="V4">
-        <v>1.606592400427285</v>
+        <v>2.054184728242748</v>
       </c>
       <c r="W4">
-        <v>0.1238237676824328</v>
+        <v>0.2337323613990504</v>
       </c>
       <c r="X4">
-        <v>0.6102551585891851</v>
+        <v>0.5572459739360327</v>
       </c>
       <c r="Y4">
-        <v>-0.4864313909067522</v>
+        <v>-0.3235136125369823</v>
       </c>
       <c r="Z4">
-        <v>0.4166146158650844</v>
+        <v>0.4551480392219407</v>
       </c>
       <c r="AA4">
-        <v>0.02718745246417431</v>
+        <v>0.04337472484751238</v>
       </c>
       <c r="AB4">
-        <v>0.06343242804314</v>
+        <v>0.05345279351989997</v>
       </c>
       <c r="AC4">
-        <v>-0.03624497557896569</v>
+        <v>-0.01007806867238759</v>
       </c>
       <c r="AD4">
-        <v>15295.4</v>
+        <v>19324.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15295.4</v>
+        <v>19324.2</v>
       </c>
       <c r="AG4">
-        <v>14242.6</v>
+        <v>18092.1</v>
       </c>
       <c r="AH4">
-        <v>0.9589171635100654</v>
+        <v>0.9698956032925116</v>
       </c>
       <c r="AI4">
-        <v>0.8163162922757524</v>
+        <v>0.818215306446491</v>
       </c>
       <c r="AJ4">
-        <v>0.9560139348498782</v>
+        <v>0.9679112342779493</v>
       </c>
       <c r="AK4">
-        <v>0.8053810442030502</v>
+        <v>0.8082098153260607</v>
       </c>
       <c r="AL4">
-        <v>5.25</v>
+        <v>4.71</v>
       </c>
       <c r="AM4">
-        <v>4.296</v>
+        <v>2.97</v>
       </c>
       <c r="AN4">
-        <v>25.42453457446808</v>
+        <v>23.48019441069259</v>
       </c>
       <c r="AO4">
-        <v>108.5333333333333</v>
+        <v>165.5414012738854</v>
       </c>
       <c r="AP4">
-        <v>23.67453457446808</v>
+        <v>21.98311057108141</v>
       </c>
       <c r="AQ4">
-        <v>132.635009310987</v>
+        <v>262.5252525252525</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DB Financial Investment Co., Ltd. (KOSE:A016610)</t>
+          <t>Hyundai Motor Securities Co.,Ltd. (KOSE:A001500)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,10 +990,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.112</v>
+        <v>0.132</v>
       </c>
       <c r="E5">
-        <v>0.106</v>
+        <v>0.0105</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1002,85 +1008,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>21.3</v>
+        <v>40.4</v>
       </c>
       <c r="L5">
-        <v>0.02075214341387373</v>
+        <v>0.05949926362297496</v>
       </c>
       <c r="M5">
-        <v>17.1884</v>
+        <v>12.9653</v>
       </c>
       <c r="N5">
-        <v>0.1299198790627362</v>
+        <v>0.06124374114312706</v>
       </c>
       <c r="O5">
-        <v>0.8069671361502346</v>
+        <v>0.3209232673267327</v>
       </c>
       <c r="P5">
-        <v>14.1984</v>
+        <v>12.9653</v>
       </c>
       <c r="Q5">
-        <v>0.1073197278911564</v>
+        <v>0.06124374114312706</v>
       </c>
       <c r="R5">
-        <v>0.6665915492957745</v>
+        <v>0.3209232673267327</v>
       </c>
       <c r="S5">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.173954527472016</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>373</v>
+        <v>753.7</v>
       </c>
       <c r="V5">
-        <v>2.819349962207105</v>
+        <v>3.560226735947095</v>
       </c>
       <c r="W5">
-        <v>0.0281336679434685</v>
+        <v>0.0483658565784748</v>
       </c>
       <c r="X5">
-        <v>0.5126577097131007</v>
+        <v>0.4672469715261893</v>
       </c>
       <c r="Y5">
-        <v>-0.4845240417696322</v>
+        <v>-0.4188811149477145</v>
       </c>
       <c r="Z5">
-        <v>0.2848816231369175</v>
+        <v>0.1569361623445662</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06348846829580546</v>
+        <v>0.05349206243865941</v>
       </c>
       <c r="AC5">
-        <v>-0.06348846829580546</v>
+        <v>-0.05349206243865941</v>
       </c>
       <c r="AD5">
-        <v>2530.5</v>
+        <v>5587.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2530.5</v>
+        <v>5587.5</v>
       </c>
       <c r="AG5">
-        <v>2157.5</v>
+        <v>4833.8</v>
       </c>
       <c r="AH5">
-        <v>0.9503154574132492</v>
+        <v>0.9634949648227342</v>
       </c>
       <c r="AI5">
-        <v>0.7728605460875939</v>
+        <v>0.855299412196914</v>
       </c>
       <c r="AJ5">
-        <v>0.942222028124727</v>
+        <v>0.9580418194430681</v>
       </c>
       <c r="AK5">
-        <v>0.7436577967737489</v>
+        <v>0.8364278174802304</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1097,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eugene Investment &amp; Securities Co.,Ltd. (KOSE:A001200)</t>
+          <t>DB Financial Investment Co., Ltd. (KOSE:A016610)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1106,10 +1112,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.214</v>
+        <v>-0.0756</v>
       </c>
       <c r="E6">
-        <v>0.00045</v>
+        <v>-0.257</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1124,28 +1130,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>36.7</v>
+        <v>8.51</v>
       </c>
       <c r="L6">
-        <v>0.0294188376753507</v>
+        <v>0.02228915662650602</v>
       </c>
       <c r="M6">
-        <v>8.9046</v>
+        <v>5.1408</v>
       </c>
       <c r="N6">
-        <v>0.05238</v>
+        <v>0.04213770491803279</v>
       </c>
       <c r="O6">
-        <v>0.2426321525885559</v>
+        <v>0.6040893066980023</v>
       </c>
       <c r="P6">
-        <v>8.9046</v>
+        <v>5.1408</v>
       </c>
       <c r="Q6">
-        <v>0.05238</v>
+        <v>0.04213770491803279</v>
       </c>
       <c r="R6">
-        <v>0.2426321525885559</v>
+        <v>0.6040893066980023</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1154,55 +1160,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>500.7</v>
+        <v>556.6</v>
       </c>
       <c r="V6">
-        <v>2.945294117647059</v>
+        <v>4.562295081967213</v>
       </c>
       <c r="W6">
-        <v>0.04578343313373254</v>
+        <v>0.01312056737588652</v>
       </c>
       <c r="X6">
-        <v>0.4943631648769586</v>
+        <v>0.4139861150676277</v>
       </c>
       <c r="Y6">
-        <v>-0.4485797317432261</v>
+        <v>-0.4008655476917412</v>
       </c>
       <c r="Z6">
-        <v>0.3089324187117704</v>
+        <v>0.1360607248494352</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06350169136858931</v>
+        <v>0.05352429860628374</v>
       </c>
       <c r="AC6">
-        <v>-0.06350169136858931</v>
+        <v>-0.05352429860628374</v>
       </c>
       <c r="AD6">
-        <v>3117.3</v>
+        <v>2799.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3117.3</v>
+        <v>2799.5</v>
       </c>
       <c r="AG6">
-        <v>2616.6</v>
+        <v>2242.9</v>
       </c>
       <c r="AH6">
-        <v>0.9482858272746632</v>
+        <v>0.958240629813452</v>
       </c>
       <c r="AI6">
-        <v>0.8136615159741073</v>
+        <v>0.7783523785692441</v>
       </c>
       <c r="AJ6">
-        <v>0.9389937558314793</v>
+        <v>0.9484121950188169</v>
       </c>
       <c r="AK6">
-        <v>0.785647800630536</v>
+        <v>0.7377717838229005</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1219,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hyundai Motor Securities Co., Ltd. (KOSE:A001500)</t>
+          <t>Korea Investment Holdings Co., Ltd. (KOSE:A071050)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,10 +1234,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.183</v>
+        <v>0.209</v>
       </c>
       <c r="E7">
-        <v>0.183</v>
+        <v>0.0444</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1246,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>70.3</v>
+        <v>593.3</v>
       </c>
       <c r="L7">
-        <v>0.09923771880293619</v>
+        <v>0.04618666168445471</v>
       </c>
       <c r="M7">
-        <v>17.6569</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N7">
-        <v>0.07744254385964912</v>
+        <v>0.03499297181327217</v>
       </c>
       <c r="O7">
-        <v>0.2511650071123755</v>
+        <v>0.1594471599528063</v>
       </c>
       <c r="P7">
-        <v>17.6569</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q7">
-        <v>0.07744254385964912</v>
+        <v>0.03499297181327217</v>
       </c>
       <c r="R7">
-        <v>0.2511650071123755</v>
+        <v>0.1594471599528063</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1276,55 +1282,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>381.7</v>
+        <v>11521.7</v>
       </c>
       <c r="V7">
-        <v>1.674122807017544</v>
+        <v>4.26192942220907</v>
       </c>
       <c r="W7">
-        <v>0.07458094631869297</v>
+        <v>0.1078158789002163</v>
       </c>
       <c r="X7">
-        <v>0.4606036924916975</v>
+        <v>0.3076088764562564</v>
       </c>
       <c r="Y7">
-        <v>-0.3860227461730046</v>
+        <v>-0.1997929975560401</v>
       </c>
       <c r="Z7">
-        <v>0.1439720347939192</v>
+        <v>0.3890973856624897</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06352915971619311</v>
+        <v>0.05362766687485078</v>
       </c>
       <c r="AC7">
-        <v>-0.06352915971619311</v>
+        <v>-0.05362766687485078</v>
       </c>
       <c r="AD7">
-        <v>3848.5</v>
+        <v>43423.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3848.5</v>
+        <v>43423.5</v>
       </c>
       <c r="AG7">
-        <v>3466.8</v>
+        <v>31901.8</v>
       </c>
       <c r="AH7">
-        <v>0.9440696676070158</v>
+        <v>0.9413921160971147</v>
       </c>
       <c r="AI7">
-        <v>0.8173689576076799</v>
+        <v>0.8733643337262016</v>
       </c>
       <c r="AJ7">
-        <v>0.9382916531341344</v>
+        <v>0.9218787927825877</v>
       </c>
       <c r="AK7">
-        <v>0.8012573092657223</v>
+        <v>0.8351671941798152</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1341,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kyobo Securities Co.,Ltd. (KOSE:A030610)</t>
+          <t>EBEST Investment &amp; Securities Co., Ltd. (KOSDAQ:A078020)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1350,10 +1356,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.407</v>
+        <v>0.0584</v>
       </c>
       <c r="E8">
-        <v>0.0925</v>
+        <v>-0.309</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1368,28 +1374,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>53.6</v>
+        <v>5.6</v>
       </c>
       <c r="L8">
-        <v>0.01724970231390596</v>
+        <v>0.006526806526806527</v>
       </c>
       <c r="M8">
-        <v>22.1328</v>
+        <v>3.7296</v>
       </c>
       <c r="N8">
-        <v>0.08367788279773157</v>
+        <v>0.0245691699604743</v>
       </c>
       <c r="O8">
-        <v>0.4129253731343284</v>
+        <v>0.6659999999999999</v>
       </c>
       <c r="P8">
-        <v>22.1328</v>
+        <v>3.7296</v>
       </c>
       <c r="Q8">
-        <v>0.08367788279773157</v>
+        <v>0.0245691699604743</v>
       </c>
       <c r="R8">
-        <v>0.4129253731343284</v>
+        <v>0.6659999999999999</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1398,55 +1404,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>102.6</v>
+        <v>60.9</v>
       </c>
       <c r="V8">
-        <v>0.3879017013232514</v>
+        <v>0.4011857707509881</v>
       </c>
       <c r="W8">
-        <v>0.04589041095890411</v>
+        <v>0.009485094850948509</v>
       </c>
       <c r="X8">
-        <v>0.4097135449678069</v>
+        <v>0.2916174097108242</v>
       </c>
       <c r="Y8">
-        <v>-0.3638231340089028</v>
+        <v>-0.2821323148598757</v>
       </c>
       <c r="Z8">
-        <v>0.7238061961332402</v>
+        <v>0.3964147107743485</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0635802170827558</v>
+        <v>0.05365088368506249</v>
       </c>
       <c r="AC8">
-        <v>-0.0635802170827558</v>
+        <v>-0.05365088368506249</v>
       </c>
       <c r="AD8">
-        <v>3883.4</v>
+        <v>2281.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>3883.4</v>
+        <v>2281.2</v>
       </c>
       <c r="AG8">
-        <v>3780.8</v>
+        <v>2220.3</v>
       </c>
       <c r="AH8">
-        <v>0.9362327924974084</v>
+        <v>0.9376078914919851</v>
       </c>
       <c r="AI8">
-        <v>0.7904013677440366</v>
+        <v>0.7677189203742344</v>
       </c>
       <c r="AJ8">
-        <v>0.9346154796924826</v>
+        <v>0.9360060705703805</v>
       </c>
       <c r="AK8">
-        <v>0.7859310688895356</v>
+        <v>0.7628586153581858</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1463,7 +1469,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Korea Investment Holdings Co., Ltd. (KOSE:A071050)</t>
+          <t>Hanyang Securities Co. Ltd. (KOSE:A001750)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1472,10 +1478,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.306</v>
+        <v>0.384</v>
       </c>
       <c r="E9">
-        <v>0.143</v>
+        <v>0.293</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1490,85 +1496,82 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>612.1</v>
+        <v>19.5</v>
       </c>
       <c r="L9">
-        <v>0.04460069950451764</v>
+        <v>0.02773431944246907</v>
       </c>
       <c r="M9">
-        <v>255.4</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.1037367993501219</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.417252082992975</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>255.4</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.1037367993501219</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.417252082992975</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>8060.3</v>
+        <v>244.6</v>
       </c>
       <c r="V9">
-        <v>3.273883021933388</v>
+        <v>2.693832599118943</v>
       </c>
       <c r="W9">
-        <v>0.1024332284624138</v>
+        <v>0.05891238670694864</v>
       </c>
       <c r="X9">
-        <v>0.4046217062217985</v>
+        <v>0.2660881640287643</v>
       </c>
       <c r="Y9">
-        <v>-0.3021884777593847</v>
+        <v>-0.2071757773218157</v>
       </c>
       <c r="Z9">
-        <v>0.4968287526427062</v>
+        <v>0.7298641171768762</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06358612427454154</v>
+        <v>0.05369487548222319</v>
       </c>
       <c r="AC9">
-        <v>-0.06358612427454154</v>
+        <v>-0.05369487548222319</v>
       </c>
       <c r="AD9">
-        <v>35605.9</v>
+        <v>1214.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>35605.9</v>
+        <v>1214.5</v>
       </c>
       <c r="AG9">
-        <v>27545.6</v>
+        <v>969.9</v>
       </c>
       <c r="AH9">
-        <v>0.9353260883841767</v>
+        <v>0.9304374473301157</v>
       </c>
       <c r="AI9">
-        <v>0.8656075266203141</v>
+        <v>0.7725335538451753</v>
       </c>
       <c r="AJ9">
-        <v>0.9179541182900331</v>
+        <v>0.9143961534835485</v>
       </c>
       <c r="AK9">
-        <v>0.8328551084396363</v>
+        <v>0.7306214689265537</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1585,7 +1588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yuanta Securities Korea Co., Ltd. (KOSE:A003470)</t>
+          <t>SK Securities Co., Ltd. (KOSE:A001510)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1594,7 +1597,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0876</v>
+        <v>0.14</v>
+      </c>
+      <c r="E10">
+        <v>0.317</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1609,28 +1615,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-7.03</v>
+        <v>18.2</v>
       </c>
       <c r="L10">
-        <v>-0.004295490651350361</v>
+        <v>0.02790127242066534</v>
       </c>
       <c r="M10">
-        <v>26.2</v>
+        <v>1.6556</v>
       </c>
       <c r="N10">
-        <v>0.06730028255843822</v>
+        <v>0.008032993692382339</v>
       </c>
       <c r="O10">
-        <v>-3.726884779516358</v>
+        <v>0.09096703296703297</v>
       </c>
       <c r="P10">
-        <v>26.2</v>
+        <v>1.6556</v>
       </c>
       <c r="Q10">
-        <v>0.06730028255843822</v>
+        <v>0.008032993692382339</v>
       </c>
       <c r="R10">
-        <v>-3.726884779516358</v>
+        <v>0.09096703296703297</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1639,55 +1645,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>595.4</v>
+        <v>212.8</v>
       </c>
       <c r="V10">
-        <v>1.529411764705882</v>
+        <v>1.032508491023775</v>
       </c>
       <c r="W10">
-        <v>-0.005283727921833898</v>
+        <v>0.0405616224648986</v>
       </c>
       <c r="X10">
-        <v>0.3740118853991187</v>
+        <v>0.2543919188429098</v>
       </c>
       <c r="Y10">
-        <v>-0.3792956133209526</v>
+        <v>-0.2138302963780113</v>
       </c>
       <c r="Z10">
-        <v>0.2675013484578546</v>
+        <v>0.2251538591640692</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06362550691112487</v>
+        <v>0.05371859561121559</v>
       </c>
       <c r="AC10">
-        <v>-0.06362550691112487</v>
+        <v>-0.05371859561121559</v>
       </c>
       <c r="AD10">
-        <v>5115.6</v>
+        <v>2600.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>5115.6</v>
+        <v>2600.7</v>
       </c>
       <c r="AG10">
-        <v>4520.200000000001</v>
+        <v>2387.9</v>
       </c>
       <c r="AH10">
-        <v>0.929281185852604</v>
+        <v>0.9265711842667806</v>
       </c>
       <c r="AI10">
-        <v>0.8235426694785646</v>
+        <v>0.8403450949980613</v>
       </c>
       <c r="AJ10">
-        <v>0.920704756085141</v>
+        <v>0.9205474171164225</v>
       </c>
       <c r="AK10">
-        <v>0.8048359240069084</v>
+        <v>0.8285565579458709</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1704,7 +1710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SK Securities Co., Ltd. (KOSE:A001510)</t>
+          <t>Kyobo Securities Co.,Ltd. (KOSE:A030610)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1713,10 +1719,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.242</v>
+        <v>0.149</v>
       </c>
       <c r="E11">
-        <v>-0.191</v>
+        <v>-0.153</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1731,85 +1737,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3.52</v>
+        <v>28.6</v>
       </c>
       <c r="L11">
-        <v>0.004317429167177726</v>
+        <v>0.01906793786252417</v>
       </c>
       <c r="M11">
-        <v>17.239</v>
+        <v>16.8221</v>
       </c>
       <c r="N11">
-        <v>0.08521502718734553</v>
+        <v>0.03875167012209168</v>
       </c>
       <c r="O11">
-        <v>4.897443181818182</v>
+        <v>0.5881853146853147</v>
       </c>
       <c r="P11">
-        <v>4.139</v>
+        <v>16.8221</v>
       </c>
       <c r="Q11">
-        <v>0.02045971329708354</v>
+        <v>0.03875167012209168</v>
       </c>
       <c r="R11">
-        <v>1.175852272727273</v>
+        <v>0.5881853146853147</v>
       </c>
       <c r="S11">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>0.7599048668716283</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>169.1</v>
+        <v>65</v>
       </c>
       <c r="V11">
-        <v>0.8358872960949085</v>
+        <v>0.1497350840820088</v>
       </c>
       <c r="W11">
-        <v>0.006676783004552352</v>
+        <v>0.02777238298698777</v>
       </c>
       <c r="X11">
-        <v>0.370036487632352</v>
+        <v>0.2490792110018319</v>
       </c>
       <c r="Y11">
-        <v>-0.3633597046277996</v>
+        <v>-0.2213068280148441</v>
       </c>
       <c r="Z11">
-        <v>0.2318669942893545</v>
+        <v>0.3117906290275642</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06363116845079056</v>
+        <v>0.05373026323230461</v>
       </c>
       <c r="AC11">
-        <v>-0.06363116845079056</v>
+        <v>-0.05373026323230461</v>
       </c>
       <c r="AD11">
-        <v>2623.6</v>
+        <v>5328.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>2623.6</v>
+        <v>5328.5</v>
       </c>
       <c r="AG11">
-        <v>2454.5</v>
+        <v>5263.5</v>
       </c>
       <c r="AH11">
-        <v>0.9284121872677731</v>
+        <v>0.924669420053448</v>
       </c>
       <c r="AI11">
-        <v>0.8515140696504495</v>
+        <v>0.7935101487691918</v>
       </c>
       <c r="AJ11">
-        <v>0.9238557663354411</v>
+        <v>0.9238100252737994</v>
       </c>
       <c r="AK11">
-        <v>0.8428914835164835</v>
+        <v>0.7914918572653042</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1826,7 +1832,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Daishin Securities Co., Ltd. (KOSE:A003540)</t>
+          <t>Daishin Securities Co.,Ltd (KOSE:A003540)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1835,10 +1841,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0379</v>
+        <v>0.00167</v>
       </c>
       <c r="E12">
-        <v>0.148</v>
+        <v>-0.151</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1853,85 +1859,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>155.6</v>
+        <v>53.2</v>
       </c>
       <c r="L12">
-        <v>0.05754863525408684</v>
+        <v>0.02924683892248488</v>
       </c>
       <c r="M12">
-        <v>84.5</v>
+        <v>59.5</v>
       </c>
       <c r="N12">
-        <v>0.1332597382116385</v>
+        <v>0.08223911541119558</v>
       </c>
       <c r="O12">
-        <v>0.5430591259640103</v>
+        <v>1.118421052631579</v>
       </c>
       <c r="P12">
-        <v>65.7</v>
+        <v>59.5</v>
       </c>
       <c r="Q12">
-        <v>0.1036114177574515</v>
+        <v>0.08223911541119558</v>
       </c>
       <c r="R12">
-        <v>0.4222365038560412</v>
+        <v>1.118421052631579</v>
       </c>
       <c r="S12">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>0.2224852071005917</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>603.4</v>
+        <v>1168.9</v>
       </c>
       <c r="V12">
-        <v>0.9515849235136413</v>
+        <v>1.615618521078093</v>
       </c>
       <c r="W12">
-        <v>0.07139907309686595</v>
+        <v>0.02749922464592164</v>
       </c>
       <c r="X12">
-        <v>0.3518273611473617</v>
+        <v>0.2477393587000851</v>
       </c>
       <c r="Y12">
-        <v>-0.2804282880504957</v>
+        <v>-0.2202401340541635</v>
       </c>
       <c r="Z12">
-        <v>0.2035472845807549</v>
+        <v>0.2021290781402791</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06365898519778984</v>
+        <v>0.05373330183637377</v>
       </c>
       <c r="AC12">
-        <v>-0.06365898519778984</v>
+        <v>-0.05373330183637377</v>
       </c>
       <c r="AD12">
-        <v>7725</v>
+        <v>8818.1</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>7725</v>
+        <v>8818.1</v>
       </c>
       <c r="AG12">
-        <v>7121.6</v>
+        <v>7649.200000000001</v>
       </c>
       <c r="AH12">
-        <v>0.9241425512315918</v>
+        <v>0.9241741427014337</v>
       </c>
       <c r="AI12">
-        <v>0.7966463508956471</v>
+        <v>0.8102413789935039</v>
       </c>
       <c r="AJ12">
-        <v>0.9182407777505576</v>
+        <v>0.9135882092992702</v>
       </c>
       <c r="AK12">
-        <v>0.7831528014515864</v>
+        <v>0.7874083834307831</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1948,7 +1954,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shinyoung Securities Co., Ltd. (KOSE:A001720)</t>
+          <t>BOOKOOK Securities Co., Ltd. (KOSE:A001270)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1957,10 +1963,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0828</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="E13">
-        <v>-0.0851</v>
+        <v>0.122</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1975,85 +1981,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>29.5</v>
+        <v>39.8</v>
       </c>
       <c r="L13">
-        <v>0.01632449781417741</v>
+        <v>0.07123679971362089</v>
       </c>
       <c r="M13">
-        <v>29.7</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>0.08139216223622912</v>
+        <v>0.06882312456985547</v>
       </c>
       <c r="O13">
-        <v>1.006779661016949</v>
+        <v>0.2512562814070352</v>
       </c>
       <c r="P13">
-        <v>23.8</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>0.06522334886270212</v>
+        <v>0.06882312456985547</v>
       </c>
       <c r="R13">
-        <v>0.8067796610169492</v>
+        <v>0.2512562814070352</v>
       </c>
       <c r="S13">
-        <v>5.900000000000002</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>0.1986531986531987</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>110.1</v>
+        <v>258.6</v>
       </c>
       <c r="V13">
-        <v>0.3017265004110715</v>
+        <v>1.779766001376462</v>
       </c>
       <c r="W13">
-        <v>0.02568567696996082</v>
+        <v>0.08050161812297735</v>
       </c>
       <c r="X13">
-        <v>0.2942458375919358</v>
+        <v>0.2430139885891779</v>
       </c>
       <c r="Y13">
-        <v>-0.268560160621975</v>
+        <v>-0.1625123704662006</v>
       </c>
       <c r="Z13">
-        <v>0.3546532166267614</v>
+        <v>0.5374182377837631</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.06377386018374342</v>
+        <v>0.05374434485688423</v>
       </c>
       <c r="AC13">
-        <v>-0.06377386018374342</v>
+        <v>-0.05374434485688423</v>
       </c>
       <c r="AD13">
-        <v>3538.2</v>
+        <v>1726.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>3538.2</v>
+        <v>1726.5</v>
       </c>
       <c r="AG13">
-        <v>3428.1</v>
+        <v>1467.9</v>
       </c>
       <c r="AH13">
-        <v>0.9065102098332095</v>
+        <v>0.9223741852762047</v>
       </c>
       <c r="AI13">
-        <v>0.7785332365172618</v>
+        <v>0.7585343350467906</v>
       </c>
       <c r="AJ13">
-        <v>0.9037964671763775</v>
+        <v>0.9099305727746095</v>
       </c>
       <c r="AK13">
-        <v>0.7730347720200242</v>
+        <v>0.7275836431226766</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2070,7 +2076,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hanyang Securities Co. Ltd. (KOSE:A001750)</t>
+          <t>Yuanta Securities Korea Co., Ltd. (KOSE:A003470)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2079,10 +2085,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.46</v>
+        <v>0.0186</v>
       </c>
       <c r="E14">
-        <v>0.6409999999999999</v>
+        <v>-0.141</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2097,82 +2103,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>26.3</v>
+        <v>40.9</v>
       </c>
       <c r="L14">
-        <v>0.03539703903095558</v>
+        <v>0.02748655913978494</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>17.3</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.04244357212953876</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0.4229828850855746</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>17.3</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.04244357212953876</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.4229828850855746</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>132</v>
+        <v>480.4</v>
       </c>
       <c r="V14">
-        <v>1.596130592503023</v>
+        <v>1.178606476938175</v>
       </c>
       <c r="W14">
-        <v>0.0745042492917847</v>
+        <v>0.03731411367575951</v>
       </c>
       <c r="X14">
-        <v>0.2832152077262263</v>
+        <v>0.2429749193335445</v>
       </c>
       <c r="Y14">
-        <v>-0.2087109584344416</v>
+        <v>-0.205660805657785</v>
       </c>
       <c r="Z14">
-        <v>0.7887306001995712</v>
+        <v>0.2649431120132471</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06380224528320233</v>
+        <v>0.05374443834604761</v>
       </c>
       <c r="AC14">
-        <v>-0.06380224528320233</v>
+        <v>-0.05374443834604761</v>
       </c>
       <c r="AD14">
-        <v>762.5</v>
+        <v>4842.2</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>762.5</v>
+        <v>4842.2</v>
       </c>
       <c r="AG14">
-        <v>630.5</v>
+        <v>4361.8</v>
       </c>
       <c r="AH14">
-        <v>0.902153336488405</v>
+        <v>0.922358947007505</v>
       </c>
       <c r="AI14">
-        <v>0.6961563042088925</v>
+        <v>0.8043922454607373</v>
       </c>
       <c r="AJ14">
-        <v>0.8840437464946719</v>
+        <v>0.9145385163752253</v>
       </c>
       <c r="AK14">
-        <v>0.6545209176788125</v>
+        <v>0.7874280143700467</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2189,7 +2198,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Samsung Securities Co., Ltd. (KOSE:A016360)</t>
+          <t>Sangsangin Investment &amp; Securities Co.,Ltd. (KOSE:A001290)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2198,10 +2207,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.26</v>
-      </c>
-      <c r="E15">
-        <v>0.187</v>
+        <v>0.383</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2216,85 +2222,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>387</v>
+        <v>3.92</v>
       </c>
       <c r="L15">
-        <v>0.04674534056456776</v>
+        <v>0.04863523573200993</v>
       </c>
       <c r="M15">
-        <v>236.645</v>
+        <v>0.041</v>
       </c>
       <c r="N15">
-        <v>0.1065248705829394</v>
+        <v>0.0006466876971608833</v>
       </c>
       <c r="O15">
-        <v>0.611485788113695</v>
+        <v>0.01045918367346939</v>
       </c>
       <c r="P15">
-        <v>236.645</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.1065248705829394</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.611485788113695</v>
+        <v>-0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>2002.1</v>
+        <v>23.9</v>
       </c>
       <c r="V15">
-        <v>0.9012379023182534</v>
+        <v>0.3769716088328076</v>
       </c>
       <c r="W15">
-        <v>0.07686654616958309</v>
+        <v>0.02352941176470588</v>
       </c>
       <c r="X15">
-        <v>0.2664680706680885</v>
+        <v>0.2318661467129875</v>
       </c>
       <c r="Y15">
-        <v>-0.1896015244985054</v>
+        <v>-0.2083367349482816</v>
       </c>
       <c r="Z15">
-        <v>0.3301009972129075</v>
+        <v>0.2656558998022412</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.06385078327677778</v>
+        <v>0.05377259758560182</v>
       </c>
       <c r="AC15">
-        <v>-0.06385078327677778</v>
+        <v>-0.05377259758560182</v>
       </c>
       <c r="AD15">
-        <v>18876</v>
+        <v>707.6</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>18876</v>
+        <v>707.6</v>
       </c>
       <c r="AG15">
-        <v>16873.9</v>
+        <v>683.7</v>
       </c>
       <c r="AH15">
-        <v>0.8947031638819766</v>
+        <v>0.9177691309987031</v>
       </c>
       <c r="AI15">
-        <v>0.8142524372357863</v>
+        <v>0.8036342986939239</v>
       </c>
       <c r="AJ15">
-        <v>0.8836630811609079</v>
+        <v>0.9151385356712622</v>
       </c>
       <c r="AK15">
-        <v>0.7966940353826033</v>
+        <v>0.7981554984823722</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2311,7 +2317,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EBEST Investment &amp; Securities Co., Ltd. (KOSDAQ:A078020)</t>
+          <t>Shinyoung Securities Co., Ltd. (KOSE:A001720)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2320,10 +2326,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.164</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="E16">
-        <v>0.151</v>
+        <v>0.119</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2338,85 +2344,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>50.6</v>
+        <v>122.9</v>
       </c>
       <c r="L16">
-        <v>0.0573826264459061</v>
+        <v>0.1652103777389434</v>
       </c>
       <c r="M16">
-        <v>21.0672</v>
+        <v>30.82</v>
       </c>
       <c r="N16">
-        <v>0.1056529588766299</v>
+        <v>0.08565869927737632</v>
       </c>
       <c r="O16">
-        <v>0.4163478260869565</v>
+        <v>0.250772986167616</v>
       </c>
       <c r="P16">
-        <v>21.0672</v>
+        <v>25.8</v>
       </c>
       <c r="Q16">
-        <v>0.1056529588766299</v>
+        <v>0.07170650361311839</v>
       </c>
       <c r="R16">
-        <v>0.4163478260869565</v>
+        <v>0.209926769731489</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.1628812459441921</v>
       </c>
       <c r="U16">
-        <v>31.1</v>
+        <v>203.8</v>
       </c>
       <c r="V16">
-        <v>0.1559679037111334</v>
+        <v>0.5664257921067259</v>
       </c>
       <c r="W16">
-        <v>0.07349310094408133</v>
+        <v>0.1279808393210455</v>
       </c>
       <c r="X16">
-        <v>0.2491046792137188</v>
+        <v>0.2238184310053264</v>
       </c>
       <c r="Y16">
-        <v>-0.1756115782696375</v>
+        <v>-0.09583759168428094</v>
       </c>
       <c r="Z16">
-        <v>0.3568162505563873</v>
+        <v>0.1695150852246833</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.06390958074855954</v>
+        <v>0.05379517011204296</v>
       </c>
       <c r="AC16">
-        <v>-0.06390958074855954</v>
+        <v>-0.05379517011204296</v>
       </c>
       <c r="AD16">
-        <v>1544.8</v>
+        <v>3828.3</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1544.8</v>
+        <v>3828.3</v>
       </c>
       <c r="AG16">
-        <v>1513.7</v>
+        <v>3624.5</v>
       </c>
       <c r="AH16">
-        <v>0.8856782479073501</v>
+        <v>0.9140899214440915</v>
       </c>
       <c r="AI16">
-        <v>0.7036210430425871</v>
+        <v>0.763933510266797</v>
       </c>
       <c r="AJ16">
-        <v>0.8836028252874905</v>
+        <v>0.9096955550535852</v>
       </c>
       <c r="AK16">
-        <v>0.6993624099057475</v>
+        <v>0.7539261570462819</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2433,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kiwoom Securities Co., Ltd. (KOSE:A039490)</t>
+          <t>Samsung Securities Co., Ltd. (KOSE:A016360)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2442,10 +2448,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.505</v>
+        <v>0.164</v>
       </c>
       <c r="E17">
-        <v>0.213</v>
+        <v>0.0959</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2460,85 +2466,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>390.7</v>
+        <v>420.1</v>
       </c>
       <c r="L17">
-        <v>0.07319769184652278</v>
+        <v>0.06450770837172165</v>
       </c>
       <c r="M17">
-        <v>132.2</v>
+        <v>112.518</v>
       </c>
       <c r="N17">
-        <v>0.07197299651567944</v>
+        <v>0.04211948790896159</v>
       </c>
       <c r="O17">
-        <v>0.3383670335295623</v>
+        <v>0.267836229469174</v>
       </c>
       <c r="P17">
-        <v>73.59999999999999</v>
+        <v>112.518</v>
       </c>
       <c r="Q17">
-        <v>0.04006968641114982</v>
+        <v>0.04211948790896159</v>
       </c>
       <c r="R17">
-        <v>0.1883798310724341</v>
+        <v>0.267836229469174</v>
       </c>
       <c r="S17">
-        <v>58.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>0.443267776096823</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1014.6</v>
+        <v>1236.4</v>
       </c>
       <c r="V17">
-        <v>0.5523736933797909</v>
+        <v>0.4628284794489781</v>
       </c>
       <c r="W17">
-        <v>0.1137839648192912</v>
+        <v>0.09756154203437065</v>
       </c>
       <c r="X17">
-        <v>0.2128489156687165</v>
+        <v>0.1550158850876711</v>
       </c>
       <c r="Y17">
-        <v>-0.09906495084942532</v>
+        <v>-0.05745434305330047</v>
       </c>
       <c r="Z17">
-        <v>0.4065318059956131</v>
+        <v>0.3074802052889768</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06407193120673169</v>
+        <v>0.05412168032559615</v>
       </c>
       <c r="AC17">
-        <v>-0.06407193120673169</v>
+        <v>-0.05412168032559615</v>
       </c>
       <c r="AD17">
-        <v>11354.7</v>
+        <v>16529.4</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>11354.7</v>
+        <v>16529.4</v>
       </c>
       <c r="AG17">
-        <v>10340.1</v>
+        <v>15293</v>
       </c>
       <c r="AH17">
-        <v>0.860758821968692</v>
+        <v>0.8608703804008165</v>
       </c>
       <c r="AI17">
-        <v>0.7850372306224462</v>
+        <v>0.7699265911462214</v>
       </c>
       <c r="AJ17">
-        <v>0.8491570104049472</v>
+        <v>0.8512947830152969</v>
       </c>
       <c r="AK17">
-        <v>0.7688206821172849</v>
+        <v>0.7558668274648583</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2555,7 +2561,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BOOKOOK Securities Co., Ltd. (KOSE:A001270)</t>
+          <t>Yuhwa Securities co.,ltd. (KOSE:A003460)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2564,10 +2570,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.06660000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="E18">
-        <v>0.0475</v>
+        <v>-0.251</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2582,85 +2588,82 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>31.2</v>
+        <v>1.24</v>
       </c>
       <c r="L18">
-        <v>0.04904118201823326</v>
+        <v>0.06739130434782609</v>
       </c>
       <c r="M18">
-        <v>10</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.0782472613458529</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.3205128205128205</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>10</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.0782472613458529</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.3205128205128205</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>204.5</v>
+        <v>11.6</v>
       </c>
       <c r="V18">
-        <v>1.600156494522692</v>
+        <v>0.13441483198146</v>
       </c>
       <c r="W18">
-        <v>0.05653198043123754</v>
+        <v>0.003528742174160501</v>
       </c>
       <c r="X18">
-        <v>0.2055399857378887</v>
+        <v>0.07394251579067515</v>
       </c>
       <c r="Y18">
-        <v>-0.1490080053066511</v>
+        <v>-0.07041377361651464</v>
       </c>
       <c r="Z18">
-        <v>0.867466593946005</v>
+        <v>0.04148816234498309</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.06411362631617069</v>
+        <v>0.05642907747835776</v>
       </c>
       <c r="AC18">
-        <v>-0.06411362631617069</v>
+        <v>-0.05642907747835776</v>
       </c>
       <c r="AD18">
-        <v>749.7</v>
+        <v>81.2</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>749.7</v>
+        <v>81.2</v>
       </c>
       <c r="AG18">
-        <v>545.2</v>
+        <v>69.60000000000001</v>
       </c>
       <c r="AH18">
-        <v>0.8543589743589745</v>
+        <v>0.4847761194029851</v>
       </c>
       <c r="AI18">
-        <v>0.6026042922594648</v>
+        <v>0.1794475138121547</v>
       </c>
       <c r="AJ18">
-        <v>0.8101040118870729</v>
+        <v>0.4464400256574728</v>
       </c>
       <c r="AK18">
-        <v>0.5244324740284726</v>
+        <v>0.1578589249262871</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2677,7 +2680,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sangsangin Investment &amp; Securities Co.,Ltd. (KOSE:A001290)</t>
+          <t>Daol Investment &amp; Securities Co., Ltd. (KOSE:A030210)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2686,7 +2689,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.00078</v>
+        <v>0.238</v>
+      </c>
+      <c r="E19">
+        <v>0.259</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2701,82 +2707,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0.923</v>
+        <v>-26.8</v>
       </c>
       <c r="L19">
-        <v>0.03238596491228071</v>
+        <v>-0.03747203579418344</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>18.4712</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.1030184049079755</v>
       </c>
       <c r="O19">
-        <v>-0</v>
+        <v>-0.6892238805970149</v>
       </c>
       <c r="P19">
-        <v>-0</v>
+        <v>6.5712</v>
       </c>
       <c r="Q19">
-        <v>-0</v>
+        <v>0.03664919129949805</v>
       </c>
       <c r="R19">
-        <v>-0</v>
+        <v>-0.2451940298507463</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>11.9</v>
+      </c>
+      <c r="T19">
+        <v>0.6442461778336004</v>
       </c>
       <c r="U19">
-        <v>2.2</v>
+        <v>688.1</v>
       </c>
       <c r="V19">
-        <v>0.03442879499217528</v>
+        <v>3.837702175125488</v>
       </c>
       <c r="W19">
-        <v>0.005655637254901961</v>
+        <v>-0.06390081068192657</v>
       </c>
       <c r="X19">
-        <v>0.1200587866589167</v>
+        <v>0.3025831385042548</v>
       </c>
       <c r="Y19">
-        <v>-0.1144031494040148</v>
+        <v>-0.3664839491861813</v>
       </c>
       <c r="Z19">
-        <v>0.07293666026871401</v>
+        <v>0.2466802331597283</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.06521656926212221</v>
+        <v>0.05773321791527113</v>
       </c>
       <c r="AC19">
-        <v>-0.06521656926212221</v>
+        <v>-0.05773321791527113</v>
       </c>
       <c r="AD19">
-        <v>139</v>
+        <v>2821.7</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>139</v>
+        <v>2821.7</v>
       </c>
       <c r="AG19">
-        <v>136.8</v>
+        <v>2133.6</v>
       </c>
       <c r="AH19">
-        <v>0.6850665352390339</v>
+        <v>0.9402532489170276</v>
       </c>
       <c r="AI19">
-        <v>0.4548429319371727</v>
+        <v>0.8205001453911021</v>
       </c>
       <c r="AJ19">
-        <v>0.6816143497757847</v>
+        <v>0.9224782740282761</v>
       </c>
       <c r="AK19">
-        <v>0.4508899143045485</v>
+        <v>0.7756007124940929</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2793,7 +2802,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yuhwa Securities co.,ltd. (KOSE:A003460)</t>
+          <t>Eugene Investment &amp; Securities Co.,Ltd. (KOSE:A001200)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2802,10 +2811,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.013</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="E20">
-        <v>-0.0495</v>
+        <v>-0.396</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2820,82 +2829,85 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>4.48</v>
+        <v>3.21</v>
       </c>
       <c r="L20">
-        <v>0.3419847328244275</v>
+        <v>0.003693051081454211</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>7.901</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.0313158937772493</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>2.461370716510904</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>4.130999999999999</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.01637336504161712</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>1.286915887850467</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.77</v>
+      </c>
+      <c r="T20">
+        <v>0.477154790532844</v>
       </c>
       <c r="U20">
-        <v>14.5</v>
+        <v>356.3</v>
       </c>
       <c r="V20">
-        <v>0.1757575757575758</v>
+        <v>1.412207689258819</v>
       </c>
       <c r="W20">
-        <v>0.01133029843196763</v>
+        <v>0.004496428071158426</v>
       </c>
       <c r="X20">
-        <v>0.09618026188511215</v>
+        <v>0.256395849591217</v>
       </c>
       <c r="Y20">
-        <v>-0.08484996345314452</v>
+        <v>-0.2518994215200586</v>
       </c>
       <c r="Z20">
-        <v>0.02482758097866155</v>
+        <v>0.2609818345593755</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.06620314929400174</v>
+        <v>0.05775628918033654</v>
       </c>
       <c r="AC20">
-        <v>-0.06620314929400174</v>
+        <v>-0.05775628918033654</v>
       </c>
       <c r="AD20">
-        <v>94.40000000000001</v>
+        <v>3216.4</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>94.40000000000001</v>
+        <v>3216.4</v>
       </c>
       <c r="AG20">
-        <v>79.90000000000001</v>
+        <v>2860.1</v>
       </c>
       <c r="AH20">
-        <v>0.5336348219332957</v>
+        <v>0.9272638164153717</v>
       </c>
       <c r="AI20">
-        <v>0.2061135371179039</v>
+        <v>0.8113412203919985</v>
       </c>
       <c r="AJ20">
-        <v>0.4919950738916256</v>
+        <v>0.9189371546073769</v>
       </c>
       <c r="AK20">
-        <v>0.1801578354002255</v>
+        <v>0.7927106430155211</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2912,7 +2924,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Daol Investment &amp; Securities Co., Ltd. (KOSE:A030210)</t>
+          <t>Hanwha Investment &amp; Securities Co., Ltd. (KOSE:A003530)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2921,10 +2933,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.402</v>
-      </c>
-      <c r="E21">
-        <v>0.311</v>
+        <v>-0.04</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2939,85 +2948,82 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>97.3</v>
+        <v>-36.5</v>
       </c>
       <c r="L21">
-        <v>0.08939728041161336</v>
+        <v>-0.03394085921517575</v>
       </c>
       <c r="M21">
-        <v>12.2764</v>
+        <v>-0</v>
       </c>
       <c r="N21">
-        <v>0.09465227447956824</v>
+        <v>-0</v>
       </c>
       <c r="O21">
-        <v>0.1261706063720452</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>10.1964</v>
+        <v>-0</v>
       </c>
       <c r="Q21">
-        <v>0.07861526599845797</v>
+        <v>-0</v>
       </c>
       <c r="R21">
-        <v>0.1047934224049332</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>2.08</v>
-      </c>
-      <c r="T21">
-        <v>0.1694307777524356</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>168.4</v>
+        <v>116.9</v>
       </c>
       <c r="V21">
-        <v>1.298380878951427</v>
+        <v>0.1908883082952319</v>
       </c>
       <c r="W21">
-        <v>0.1727627840909091</v>
+        <v>-0.03213311030900607</v>
       </c>
       <c r="X21">
-        <v>0.5302338614202502</v>
+        <v>0.1831237142733568</v>
       </c>
       <c r="Y21">
-        <v>-0.3574710773293411</v>
+        <v>-0.2152568245823628</v>
       </c>
       <c r="Z21">
-        <v>0.4194866260695291</v>
+        <v>0.168955223880597</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.06897520408959962</v>
+        <v>0.05782430593573124</v>
       </c>
       <c r="AC21">
-        <v>-0.06897520408959962</v>
+        <v>-0.05782430593573124</v>
       </c>
       <c r="AD21">
-        <v>2579.2</v>
+        <v>4903.2</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>2579.2</v>
+        <v>4903.2</v>
       </c>
       <c r="AG21">
-        <v>2410.8</v>
+        <v>4786.3</v>
       </c>
       <c r="AH21">
-        <v>0.9521207870353281</v>
+        <v>0.8889694684168541</v>
       </c>
       <c r="AI21">
-        <v>0.7846429983876365</v>
+        <v>0.8057714745854627</v>
       </c>
       <c r="AJ21">
-        <v>0.9489470576658139</v>
+        <v>0.8865652842350937</v>
       </c>
       <c r="AK21">
-        <v>0.7730143970244011</v>
+        <v>0.8019670922556213</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3034,7 +3040,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hanwha Investment &amp; Securities Co., Ltd. (KOSE:A003530)</t>
+          <t>Kiwoom Securities Co., Ltd. (KOSE:A039490)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3042,12 +3048,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D22">
-        <v>0.0527</v>
-      </c>
-      <c r="E22">
-        <v>0.269</v>
-      </c>
       <c r="G22">
         <v>0</v>
       </c>
@@ -3061,28 +3061,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>39.3</v>
+        <v>566.1</v>
       </c>
       <c r="L22">
-        <v>0.03026336054212228</v>
+        <v>0.1088591042824452</v>
       </c>
       <c r="M22">
-        <v>30.3159</v>
+        <v>66.3</v>
       </c>
       <c r="N22">
-        <v>0.07478021706956094</v>
+        <v>0.03102044635755392</v>
       </c>
       <c r="O22">
-        <v>0.7713969465648857</v>
+        <v>0.1171171171171171</v>
       </c>
       <c r="P22">
-        <v>30.3159</v>
+        <v>66.3</v>
       </c>
       <c r="Q22">
-        <v>0.07478021706956094</v>
+        <v>0.03102044635755392</v>
       </c>
       <c r="R22">
-        <v>0.7713969465648857</v>
+        <v>0.1171171171171171</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3091,55 +3091,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>179</v>
+        <v>972</v>
       </c>
       <c r="V22">
-        <v>0.4415392205229403</v>
+        <v>0.454779394563234</v>
       </c>
       <c r="W22">
-        <v>0.02963577407435337</v>
+        <v>0.1836079398028023</v>
       </c>
       <c r="X22">
-        <v>0.3784586327527228</v>
+        <v>0.1615182029263536</v>
       </c>
       <c r="Y22">
-        <v>-0.3488228586783695</v>
+        <v>0.02208973687644869</v>
       </c>
       <c r="Z22">
-        <v>0.1933418693982074</v>
+        <v>0.3874084614066586</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.06899140469060373</v>
+        <v>0.05786054703195449</v>
       </c>
       <c r="AC22">
-        <v>-0.06899140469060373</v>
+        <v>-0.05786054703195449</v>
       </c>
       <c r="AD22">
-        <v>5405</v>
+        <v>14124</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>5405</v>
+        <v>14124</v>
       </c>
       <c r="AG22">
-        <v>5226</v>
+        <v>13152</v>
       </c>
       <c r="AH22">
-        <v>0.9302285556932398</v>
+        <v>0.8685652438611919</v>
       </c>
       <c r="AI22">
-        <v>0.8241465013799307</v>
+        <v>0.7876114583972296</v>
       </c>
       <c r="AJ22">
-        <v>0.9280107966047519</v>
+        <v>0.8602094275081267</v>
       </c>
       <c r="AK22">
-        <v>0.8192121392629285</v>
+        <v>0.7754396929372018</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Meritz Securities Co., Ltd. (KOSE:A008560)</t>
+          <t>NH Investment &amp; Securities Co., Ltd. (KOSE:A005940)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.61</v>
+        <v>-0.0395</v>
       </c>
       <c r="E23">
-        <v>0.211</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3183,85 +3183,85 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>586.4</v>
+        <v>398.8</v>
       </c>
       <c r="L23">
-        <v>0.01776786634104365</v>
+        <v>0.07463971551562792</v>
       </c>
       <c r="M23">
-        <v>205.812</v>
+        <v>182.6</v>
       </c>
       <c r="N23">
-        <v>0.07844042991081637</v>
+        <v>0.06521428571428571</v>
       </c>
       <c r="O23">
-        <v>0.3509754433833561</v>
+        <v>0.4578736208625878</v>
       </c>
       <c r="P23">
-        <v>37.212</v>
+        <v>182.6</v>
       </c>
       <c r="Q23">
-        <v>0.01418248342099245</v>
+        <v>0.06521428571428571</v>
       </c>
       <c r="R23">
-        <v>0.06345839017735334</v>
+        <v>0.4578736208625878</v>
       </c>
       <c r="S23">
-        <v>168.6</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>0.8191942160806951</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>669.3</v>
+        <v>1362.5</v>
       </c>
       <c r="V23">
-        <v>0.25508804024697</v>
+        <v>0.4866071428571428</v>
       </c>
       <c r="W23">
-        <v>0.1426208775172682</v>
+        <v>0.07837742227113714</v>
       </c>
       <c r="X23">
-        <v>0.2397031072437286</v>
+        <v>0.1477238896204222</v>
       </c>
       <c r="Y23">
-        <v>-0.09708222972646038</v>
+        <v>-0.0693464673492851</v>
       </c>
       <c r="Z23">
-        <v>1.250574068039378</v>
+        <v>0.249047949770902</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.06902848982277364</v>
+        <v>0.05789157882362864</v>
       </c>
       <c r="AC23">
-        <v>-0.06902848982277364</v>
+        <v>-0.05789157882362864</v>
       </c>
       <c r="AD23">
-        <v>19262.1</v>
+        <v>16003.8</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>19262.1</v>
+        <v>16003.8</v>
       </c>
       <c r="AG23">
-        <v>18592.8</v>
+        <v>14641.3</v>
       </c>
       <c r="AH23">
-        <v>0.880114594327855</v>
+        <v>0.8510939278230996</v>
       </c>
       <c r="AI23">
-        <v>0.8256683712616432</v>
+        <v>0.7404675867876427</v>
       </c>
       <c r="AJ23">
-        <v>0.8763326828992393</v>
+        <v>0.8394615080297914</v>
       </c>
       <c r="AK23">
-        <v>0.8205191572741154</v>
+        <v>0.7230057381015871</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NH Investment &amp; Securities Co., Ltd. (KOSE:A005940)</t>
+          <t>Korea Asset Investment Securities Co., Ltd. (KOSDAQ:A190650)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3286,12 +3286,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D24">
-        <v>0.0915</v>
-      </c>
-      <c r="E24">
-        <v>0.0581</v>
-      </c>
       <c r="G24">
         <v>0</v>
       </c>
@@ -3305,325 +3299,87 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>294.7</v>
+        <v>0.3</v>
       </c>
       <c r="L24">
-        <v>0.03439582628181935</v>
+        <v>0.002407704654895666</v>
       </c>
       <c r="M24">
-        <v>231.1</v>
+        <v>-0</v>
       </c>
       <c r="N24">
-        <v>0.09522043675319324</v>
+        <v>-0</v>
       </c>
       <c r="O24">
-        <v>0.7841873091279267</v>
+        <v>-0</v>
       </c>
       <c r="P24">
-        <v>231.1</v>
+        <v>-0</v>
       </c>
       <c r="Q24">
-        <v>0.09522043675319324</v>
+        <v>-0</v>
       </c>
       <c r="R24">
-        <v>0.7841873091279267</v>
+        <v>-0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
       <c r="U24">
-        <v>1193.4</v>
+        <v>28.8</v>
       </c>
       <c r="V24">
-        <v>0.4917181705809642</v>
+        <v>0.9863013698630138</v>
       </c>
       <c r="W24">
-        <v>0.05410118960199736</v>
+        <v>0.0048</v>
       </c>
       <c r="X24">
-        <v>0.2375013250579086</v>
+        <v>0.07607284030911267</v>
       </c>
       <c r="Y24">
-        <v>-0.1834001354559113</v>
+        <v>-0.07127284030911267</v>
       </c>
       <c r="Z24">
-        <v>0.3678094305927604</v>
+        <v>1.840472673559823</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.06902951262283588</v>
+        <v>0.05848152617665471</v>
       </c>
       <c r="AC24">
-        <v>-0.06902951262283588</v>
+        <v>-0.05848152617665471</v>
       </c>
       <c r="AD24">
-        <v>17586.6</v>
+        <v>31.5</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>17586.6</v>
+        <v>31.5</v>
       </c>
       <c r="AG24">
-        <v>16393.2</v>
+        <v>2.699999999999999</v>
       </c>
       <c r="AH24">
-        <v>0.8787324619258904</v>
+        <v>0.5189456342668863</v>
       </c>
       <c r="AI24">
-        <v>0.7754814073365287</v>
+        <v>0.3227459016393443</v>
       </c>
       <c r="AJ24">
-        <v>0.8710428156980266</v>
+        <v>0.08463949843260186</v>
       </c>
       <c r="AK24">
-        <v>0.76301030025739</v>
+        <v>0.03924418604651162</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Woori Investment Bank Co.,Ltd. (KOSE:A010050)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>0.194</v>
-      </c>
-      <c r="E25">
-        <v>0.283</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>56.9</v>
-      </c>
-      <c r="L25">
-        <v>0.3232954545454546</v>
-      </c>
-      <c r="M25">
-        <v>12.2374</v>
-      </c>
-      <c r="N25">
-        <v>0.02378965785381027</v>
-      </c>
-      <c r="O25">
-        <v>0.2150685413005273</v>
-      </c>
-      <c r="P25">
-        <v>12.2374</v>
-      </c>
-      <c r="Q25">
-        <v>0.02378965785381027</v>
-      </c>
-      <c r="R25">
-        <v>0.2150685413005273</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>215.8</v>
-      </c>
-      <c r="V25">
-        <v>0.4195178849144635</v>
-      </c>
-      <c r="W25">
-        <v>0.1146483981462825</v>
-      </c>
-      <c r="X25">
-        <v>0.09648199252215534</v>
-      </c>
-      <c r="Y25">
-        <v>0.01816640562412715</v>
-      </c>
-      <c r="Z25">
-        <v>0.1960129190333</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0.06928280615696812</v>
-      </c>
-      <c r="AC25">
-        <v>-0.06928280615696812</v>
-      </c>
-      <c r="AD25">
-        <v>595.3</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>595.3</v>
-      </c>
-      <c r="AG25">
-        <v>379.4999999999999</v>
-      </c>
-      <c r="AH25">
-        <v>0.5364512931422908</v>
-      </c>
-      <c r="AI25">
-        <v>0.5678176268599771</v>
-      </c>
-      <c r="AJ25">
-        <v>0.4245441324532945</v>
-      </c>
-      <c r="AK25">
-        <v>0.4558011049723757</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Korea Asset Investment Securities Co., Ltd. (KOSDAQ:A190650)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>4.52</v>
-      </c>
-      <c r="L26">
-        <v>0.02676139727649497</v>
-      </c>
-      <c r="M26">
-        <v>-0</v>
-      </c>
-      <c r="N26">
-        <v>-0</v>
-      </c>
-      <c r="O26">
-        <v>-0</v>
-      </c>
-      <c r="P26">
-        <v>-0</v>
-      </c>
-      <c r="Q26">
-        <v>-0</v>
-      </c>
-      <c r="R26">
-        <v>-0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>17.2</v>
-      </c>
-      <c r="V26">
-        <v>0.4586666666666667</v>
-      </c>
-      <c r="W26">
-        <v>0.06083445491251682</v>
-      </c>
-      <c r="X26">
-        <v>0.08351393401693084</v>
-      </c>
-      <c r="Y26">
-        <v>-0.02267947910441402</v>
-      </c>
-      <c r="Z26">
-        <v>1.463604852686309</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0.06940305483055931</v>
-      </c>
-      <c r="AC26">
-        <v>-0.06940305483055931</v>
-      </c>
-      <c r="AD26">
-        <v>22.4</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>22.4</v>
-      </c>
-      <c r="AG26">
-        <v>5.199999999999999</v>
-      </c>
-      <c r="AH26">
-        <v>0.3739565943238731</v>
-      </c>
-      <c r="AI26">
-        <v>0.2638398115429917</v>
-      </c>
-      <c r="AJ26">
-        <v>0.1217798594847775</v>
-      </c>
-      <c r="AK26">
-        <v>0.07680945347119644</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/south_korea/south_korea_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.06370000000000001</v>
+        <v>0.109</v>
       </c>
       <c r="E2">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.0173721864750507</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.01733181442627876</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.01573258055632057</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01252321949785255</v>
       </c>
       <c r="K2">
-        <v>506.7</v>
+        <v>2846.43</v>
       </c>
       <c r="L2">
-        <v>0.07490243614001892</v>
+        <v>0.04454116697128264</v>
       </c>
       <c r="M2">
-        <v>251.6</v>
+        <v>938.9463000000001</v>
       </c>
       <c r="N2">
-        <v>0.07761120365229193</v>
+        <v>0.06093176420200132</v>
       </c>
       <c r="O2">
-        <v>0.4965462798500099</v>
+        <v>0.329868045235611</v>
       </c>
       <c r="P2">
-        <v>212.4</v>
+        <v>765.8863</v>
       </c>
       <c r="Q2">
-        <v>0.06551915602443087</v>
+        <v>0.04970124855611364</v>
       </c>
       <c r="R2">
-        <v>0.4191829484902309</v>
+        <v>0.2690690795136364</v>
       </c>
       <c r="S2">
-        <v>39.20000000000002</v>
+        <v>173.06</v>
       </c>
       <c r="T2">
-        <v>0.1558028616852147</v>
+        <v>0.1843129899974045</v>
       </c>
       <c r="U2">
-        <v>2211.1</v>
+        <v>18363.335</v>
       </c>
       <c r="V2">
-        <v>0.6820593497439693</v>
+        <v>1.191666017728978</v>
       </c>
       <c r="W2">
-        <v>0.09038691378725985</v>
+        <v>0.05412886268183462</v>
       </c>
       <c r="X2">
-        <v>0.1606542382405337</v>
+        <v>0.3079113212629258</v>
       </c>
       <c r="Y2">
-        <v>-0.0702673244532738</v>
+        <v>-0.2537824585810912</v>
       </c>
       <c r="Z2">
-        <v>0.3345995568217791</v>
+        <v>0.3322733027986888</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06035802808004222</v>
+        <v>0.05803889250325271</v>
       </c>
       <c r="AC2">
-        <v>-0.06035802808004222</v>
+        <v>-0.05752746862746933</v>
       </c>
       <c r="AD2">
-        <v>21367.9</v>
+        <v>169867.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21367.9</v>
+        <v>169867.5</v>
       </c>
       <c r="AG2">
-        <v>19156.8</v>
+        <v>151504.165</v>
       </c>
       <c r="AH2">
-        <v>0.868271453938894</v>
+        <v>0.9168284511918082</v>
       </c>
       <c r="AI2">
-        <v>0.7803601622958064</v>
+        <v>0.7863806514273758</v>
       </c>
       <c r="AJ2">
-        <v>0.8552677399480325</v>
+        <v>0.9076781861841219</v>
       </c>
       <c r="AK2">
-        <v>0.7610663064637877</v>
+        <v>0.7665334764932275</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>62.71</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-86.42000000000002</v>
+      </c>
+      <c r="AN2">
+        <v>152.2792469744509</v>
+      </c>
+      <c r="AO2">
+        <v>16.03253069685855</v>
+      </c>
+      <c r="AP2">
+        <v>135.8172702823846</v>
+      </c>
+      <c r="AQ2">
+        <v>-11.63388104605415</v>
       </c>
     </row>
     <row r="3">
@@ -701,117 +713,2673 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Daou Technology Inc. (KOSE:A023590)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.3</v>
+      </c>
+      <c r="E3">
+        <v>0.13</v>
+      </c>
+      <c r="G3">
+        <v>0.07005969374513366</v>
+      </c>
+      <c r="H3">
+        <v>0.06972488969634051</v>
+      </c>
+      <c r="I3">
+        <v>0.07753698416818064</v>
+      </c>
+      <c r="J3">
+        <v>0.05478870335617882</v>
+      </c>
+      <c r="K3">
+        <v>165.9</v>
+      </c>
+      <c r="L3">
+        <v>0.02152867895146639</v>
+      </c>
+      <c r="M3">
+        <v>23.0256</v>
+      </c>
+      <c r="N3">
+        <v>0.04411034482758622</v>
+      </c>
+      <c r="O3">
+        <v>0.1387920433996384</v>
+      </c>
+      <c r="P3">
+        <v>23.0256</v>
+      </c>
+      <c r="Q3">
+        <v>0.04411034482758622</v>
+      </c>
+      <c r="R3">
+        <v>0.1387920433996384</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>242.4</v>
+      </c>
+      <c r="V3">
+        <v>0.464367816091954</v>
+      </c>
+      <c r="W3">
+        <v>0.0863253200124883</v>
+      </c>
+      <c r="X3">
+        <v>0.07464996303424576</v>
+      </c>
+      <c r="Y3">
+        <v>0.01167535697824254</v>
+      </c>
+      <c r="Z3">
+        <v>0.3866668673761747</v>
+      </c>
+      <c r="AA3">
+        <v>0.02118497629433617</v>
+      </c>
+      <c r="AB3">
+        <v>0.06293666872084562</v>
+      </c>
+      <c r="AC3">
+        <v>-0.04175169242650945</v>
+      </c>
+      <c r="AD3">
+        <v>343.6</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>343.6</v>
+      </c>
+      <c r="AG3">
+        <v>101.2</v>
+      </c>
+      <c r="AH3">
+        <v>0.3969500924214418</v>
+      </c>
+      <c r="AI3">
+        <v>0.06837810945273633</v>
+      </c>
+      <c r="AJ3">
+        <v>0.162387676508344</v>
+      </c>
+      <c r="AK3">
+        <v>0.02116003847279723</v>
+      </c>
+      <c r="AL3">
+        <v>55.7</v>
+      </c>
+      <c r="AM3">
+        <v>52.37</v>
+      </c>
+      <c r="AN3">
+        <v>0.5295114809677917</v>
+      </c>
+      <c r="AO3">
+        <v>10.72710951526032</v>
+      </c>
+      <c r="AP3">
+        <v>0.1559562336261366</v>
+      </c>
+      <c r="AQ3">
+        <v>11.40920374260072</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Daou Data Corp. (KOSDAQ:A032190)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.282</v>
+      </c>
+      <c r="E4">
+        <v>0.2</v>
+      </c>
+      <c r="G4">
+        <v>0.07053890586154436</v>
+      </c>
+      <c r="H4">
+        <v>0.07053890586154436</v>
+      </c>
+      <c r="I4">
+        <v>0.05045207732934236</v>
+      </c>
+      <c r="J4">
+        <v>0.03457314544060459</v>
+      </c>
+      <c r="K4">
+        <v>56.4</v>
+      </c>
+      <c r="L4">
+        <v>0.006975967544434687</v>
+      </c>
+      <c r="M4">
+        <v>7.276999999999999</v>
+      </c>
+      <c r="N4">
+        <v>0.02762718299164768</v>
+      </c>
+      <c r="O4">
+        <v>0.1290248226950355</v>
+      </c>
+      <c r="P4">
+        <v>7.276999999999999</v>
+      </c>
+      <c r="Q4">
+        <v>0.02762718299164768</v>
+      </c>
+      <c r="R4">
+        <v>0.1290248226950355</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>345.1</v>
+      </c>
+      <c r="V4">
+        <v>1.310174639331815</v>
+      </c>
+      <c r="W4">
+        <v>0.06039190491487311</v>
+      </c>
+      <c r="X4">
+        <v>0.09470273813729096</v>
+      </c>
+      <c r="Y4">
+        <v>-0.03431083322241785</v>
+      </c>
+      <c r="Z4">
+        <v>0.4272141698415298</v>
+      </c>
+      <c r="AA4">
+        <v>0.01477013762821836</v>
+      </c>
+      <c r="AB4">
+        <v>0.06143118794740209</v>
+      </c>
+      <c r="AC4">
+        <v>-0.04666105031918373</v>
+      </c>
+      <c r="AD4">
+        <v>538</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>538</v>
+      </c>
+      <c r="AG4">
+        <v>192.9</v>
+      </c>
+      <c r="AH4">
+        <v>0.6713251809333666</v>
+      </c>
+      <c r="AI4">
+        <v>0.1002777208253341</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4227481919789612</v>
+      </c>
+      <c r="AK4">
+        <v>0.03842629482071713</v>
+      </c>
+      <c r="AL4">
+        <v>7.01</v>
+      </c>
+      <c r="AM4">
+        <v>-138.79</v>
+      </c>
+      <c r="AN4">
+        <v>1.153021860265752</v>
+      </c>
+      <c r="AO4">
+        <v>58.18830242510699</v>
+      </c>
+      <c r="AP4">
+        <v>0.4134162023146163</v>
+      </c>
+      <c r="AQ4">
+        <v>-2.938972548454499</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hyundai Motor Securities Co.,Ltd. (KOSE:A001500)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.134</v>
+      </c>
+      <c r="E5">
+        <v>-0.116</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>27.6</v>
+      </c>
+      <c r="L5">
+        <v>0.03241338813857898</v>
+      </c>
+      <c r="M5">
+        <v>9.6685</v>
+      </c>
+      <c r="N5">
+        <v>0.06054164057608016</v>
+      </c>
+      <c r="O5">
+        <v>0.3503079710144927</v>
+      </c>
+      <c r="P5">
+        <v>9.6685</v>
+      </c>
+      <c r="Q5">
+        <v>0.06054164057608016</v>
+      </c>
+      <c r="R5">
+        <v>0.3503079710144927</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>479.5</v>
+      </c>
+      <c r="V5">
+        <v>3.002504696305573</v>
+      </c>
+      <c r="W5">
+        <v>0.03002610966057441</v>
+      </c>
+      <c r="X5">
+        <v>0.5850063994405088</v>
+      </c>
+      <c r="Y5">
+        <v>-0.5549802897799344</v>
+      </c>
+      <c r="Z5">
+        <v>0.1473387320044297</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.05722266802783447</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05722266802783447</v>
+      </c>
+      <c r="AD5">
+        <v>5731.5</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>5731.5</v>
+      </c>
+      <c r="AG5">
+        <v>5252</v>
+      </c>
+      <c r="AH5">
+        <v>0.9728917707767518</v>
+      </c>
+      <c r="AI5">
+        <v>0.8527875730928894</v>
+      </c>
+      <c r="AJ5">
+        <v>0.9704898645527283</v>
+      </c>
+      <c r="AK5">
+        <v>0.8414778735540104</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LS SECURITIES Co., Ltd. (KOSDAQ:A078020)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.04389999999999999</v>
+      </c>
+      <c r="E6">
+        <v>-0.0224</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>25.1</v>
+      </c>
+      <c r="L6">
+        <v>0.02527184857027789</v>
+      </c>
+      <c r="M6">
+        <v>54.3456</v>
+      </c>
+      <c r="N6">
+        <v>0.4158041315990819</v>
+      </c>
+      <c r="O6">
+        <v>2.165163346613546</v>
+      </c>
+      <c r="P6">
+        <v>5.7456</v>
+      </c>
+      <c r="Q6">
+        <v>0.04396021423106351</v>
+      </c>
+      <c r="R6">
+        <v>0.2289083665338645</v>
+      </c>
+      <c r="S6">
+        <v>48.6</v>
+      </c>
+      <c r="T6">
+        <v>0.8942766295707472</v>
+      </c>
+      <c r="U6">
+        <v>109.7</v>
+      </c>
+      <c r="V6">
+        <v>0.839326702371844</v>
+      </c>
+      <c r="W6">
+        <v>0.04010225275603132</v>
+      </c>
+      <c r="X6">
+        <v>0.4750905257905329</v>
+      </c>
+      <c r="Y6">
+        <v>-0.4349882730345016</v>
+      </c>
+      <c r="Z6">
+        <v>0.3412472083834394</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.0572796120125901</v>
+      </c>
+      <c r="AC6">
+        <v>-0.0572796120125901</v>
+      </c>
+      <c r="AD6">
+        <v>3699</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>3699</v>
+      </c>
+      <c r="AG6">
+        <v>3589.3</v>
+      </c>
+      <c r="AH6">
+        <v>0.9658720004177873</v>
+      </c>
+      <c r="AI6">
+        <v>0.8464143517459155</v>
+      </c>
+      <c r="AJ6">
+        <v>0.9648655913978496</v>
+      </c>
+      <c r="AK6">
+        <v>0.8424598051871847</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sangsangin Investment &amp; Securities Co.,Ltd. (KOSE:A001290)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.672</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-25.2</v>
+      </c>
+      <c r="L7">
+        <v>-0.1341138903672166</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>4.17</v>
+      </c>
+      <c r="V7">
+        <v>0.1362745098039216</v>
+      </c>
+      <c r="W7">
+        <v>-0.145748987854251</v>
+      </c>
+      <c r="X7">
+        <v>0.4686880380328749</v>
+      </c>
+      <c r="Y7">
+        <v>-0.6144370258871259</v>
+      </c>
+      <c r="Z7">
+        <v>0.2193555918748541</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05728385182446925</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05728385182446925</v>
+      </c>
+      <c r="AD7">
+        <v>852.5</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>852.5</v>
+      </c>
+      <c r="AG7">
+        <v>848.33</v>
+      </c>
+      <c r="AH7">
+        <v>0.9653493375608652</v>
+      </c>
+      <c r="AI7">
+        <v>0.8513081685640104</v>
+      </c>
+      <c r="AJ7">
+        <v>0.9651849407802668</v>
+      </c>
+      <c r="AK7">
+        <v>0.8506864013316888</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DB Financial Investment Co., Ltd. (KOSE:A016610)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0261</v>
+      </c>
+      <c r="E8">
+        <v>-0.0583</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>20.3</v>
+      </c>
+      <c r="L8">
+        <v>0.03035740989980559</v>
+      </c>
+      <c r="M8">
+        <v>6.5322</v>
+      </c>
+      <c r="N8">
+        <v>0.04649252669039147</v>
+      </c>
+      <c r="O8">
+        <v>0.3217832512315271</v>
+      </c>
+      <c r="P8">
+        <v>6.0952</v>
+      </c>
+      <c r="Q8">
+        <v>0.04338220640569395</v>
+      </c>
+      <c r="R8">
+        <v>0.300256157635468</v>
+      </c>
+      <c r="S8">
+        <v>0.4370000000000003</v>
+      </c>
+      <c r="T8">
+        <v>0.06689936009307741</v>
+      </c>
+      <c r="U8">
+        <v>531.5</v>
+      </c>
+      <c r="V8">
+        <v>3.782918149466192</v>
+      </c>
+      <c r="W8">
+        <v>0.02950581395348837</v>
+      </c>
+      <c r="X8">
+        <v>0.3936641437246258</v>
+      </c>
+      <c r="Y8">
+        <v>-0.3641583297711374</v>
+      </c>
+      <c r="Z8">
+        <v>0.22815517417858</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.05734532661694421</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05734532661694421</v>
+      </c>
+      <c r="AD8">
+        <v>3186.6</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>3186.6</v>
+      </c>
+      <c r="AG8">
+        <v>2655.1</v>
+      </c>
+      <c r="AH8">
+        <v>0.9577710318295212</v>
+      </c>
+      <c r="AI8">
+        <v>0.7769920998732078</v>
+      </c>
+      <c r="AJ8">
+        <v>0.9497424524252397</v>
+      </c>
+      <c r="AK8">
+        <v>0.7437879933888002</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SK Securities Co., Ltd. (KOSE:A001510)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0888</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>-54.6</v>
+      </c>
+      <c r="L9">
+        <v>-0.09426795580110496</v>
+      </c>
+      <c r="M9">
+        <v>0.8278</v>
+      </c>
+      <c r="N9">
+        <v>0.00638242097147263</v>
+      </c>
+      <c r="O9">
+        <v>-0.01516117216117216</v>
+      </c>
+      <c r="P9">
+        <v>0.8278</v>
+      </c>
+      <c r="Q9">
+        <v>0.00638242097147263</v>
+      </c>
+      <c r="R9">
+        <v>-0.01516117216117216</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>174.9</v>
+      </c>
+      <c r="V9">
+        <v>1.348496530454896</v>
+      </c>
+      <c r="W9">
+        <v>-0.1125773195876289</v>
+      </c>
+      <c r="X9">
+        <v>0.340327015502067</v>
+      </c>
+      <c r="Y9">
+        <v>-0.4529043350896959</v>
+      </c>
+      <c r="Z9">
+        <v>0.2020335908750022</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.05740839606711671</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05740839606711671</v>
+      </c>
+      <c r="AD9">
+        <v>2464.1</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>2464.1</v>
+      </c>
+      <c r="AG9">
+        <v>2289.2</v>
+      </c>
+      <c r="AH9">
+        <v>0.9499961446526333</v>
+      </c>
+      <c r="AI9">
+        <v>0.8463916463435579</v>
+      </c>
+      <c r="AJ9">
+        <v>0.9463805862168755</v>
+      </c>
+      <c r="AK9">
+        <v>0.836573600350826</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BOOKOOK Securities Co., Ltd. (KOSE:A001270)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.00582</v>
+      </c>
+      <c r="E10">
+        <v>0.112</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>31.4</v>
+      </c>
+      <c r="L10">
+        <v>0.06584189557559236</v>
+      </c>
+      <c r="M10">
+        <v>10.3</v>
+      </c>
+      <c r="N10">
+        <v>0.06692657569850552</v>
+      </c>
+      <c r="O10">
+        <v>0.3280254777070064</v>
+      </c>
+      <c r="P10">
+        <v>10.3</v>
+      </c>
+      <c r="Q10">
+        <v>0.06692657569850552</v>
+      </c>
+      <c r="R10">
+        <v>0.3280254777070064</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>247.5</v>
+      </c>
+      <c r="V10">
+        <v>1.608187134502924</v>
+      </c>
+      <c r="W10">
+        <v>0.05713245997088792</v>
+      </c>
+      <c r="X10">
+        <v>0.330230778663142</v>
+      </c>
+      <c r="Y10">
+        <v>-0.2730983186922541</v>
+      </c>
+      <c r="Z10">
+        <v>0.2363816604708798</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.05742304302858819</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05742304302858819</v>
+      </c>
+      <c r="AD10">
+        <v>2816.6</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>2816.6</v>
+      </c>
+      <c r="AG10">
+        <v>2569.1</v>
+      </c>
+      <c r="AH10">
+        <v>0.9481905403130786</v>
+      </c>
+      <c r="AI10">
+        <v>0.8275598648450124</v>
+      </c>
+      <c r="AJ10">
+        <v>0.9434814542783694</v>
+      </c>
+      <c r="AK10">
+        <v>0.8140367553865653</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yuanta Securities Korea Co., Ltd. (KOSE:A003470)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.0138</v>
+      </c>
+      <c r="E11">
+        <v>0.0123</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>60.2</v>
+      </c>
+      <c r="L11">
+        <v>0.03548482169171824</v>
+      </c>
+      <c r="M11">
+        <v>28.6</v>
+      </c>
+      <c r="N11">
+        <v>0.07771739130434784</v>
+      </c>
+      <c r="O11">
+        <v>0.4750830564784053</v>
+      </c>
+      <c r="P11">
+        <v>28.6</v>
+      </c>
+      <c r="Q11">
+        <v>0.07771739130434784</v>
+      </c>
+      <c r="R11">
+        <v>0.4750830564784053</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>584</v>
+      </c>
+      <c r="V11">
+        <v>1.58695652173913</v>
+      </c>
+      <c r="W11">
+        <v>0.05112526539278132</v>
+      </c>
+      <c r="X11">
+        <v>0.3218048681818001</v>
+      </c>
+      <c r="Y11">
+        <v>-0.2706796027890188</v>
+      </c>
+      <c r="Z11">
+        <v>0.3062661347101619</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.05743610170914239</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05743610170914239</v>
+      </c>
+      <c r="AD11">
+        <v>6520.9</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>6520.9</v>
+      </c>
+      <c r="AG11">
+        <v>5936.9</v>
+      </c>
+      <c r="AH11">
+        <v>0.9465807313214011</v>
+      </c>
+      <c r="AI11">
+        <v>0.8421888722425996</v>
+      </c>
+      <c r="AJ11">
+        <v>0.9416326983774524</v>
+      </c>
+      <c r="AK11">
+        <v>0.8293149689892161</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Korea Investment Holdings Co., Ltd. (KOSE:A071050)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.109</v>
+      </c>
+      <c r="E12">
+        <v>0.0548</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>690.9</v>
+      </c>
+      <c r="L12">
+        <v>0.05362798062593144</v>
+      </c>
+      <c r="M12">
+        <v>118.1</v>
+      </c>
+      <c r="N12">
+        <v>0.04296576563466366</v>
+      </c>
+      <c r="O12">
+        <v>0.1709364596902591</v>
+      </c>
+      <c r="P12">
+        <v>118.1</v>
+      </c>
+      <c r="Q12">
+        <v>0.04296576563466366</v>
+      </c>
+      <c r="R12">
+        <v>0.1709364596902591</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>7546.3</v>
+      </c>
+      <c r="V12">
+        <v>2.745406919634737</v>
+      </c>
+      <c r="W12">
+        <v>0.1103744648220333</v>
+      </c>
+      <c r="X12">
+        <v>0.3170721989869353</v>
+      </c>
+      <c r="Y12">
+        <v>-0.206697734164902</v>
+      </c>
+      <c r="Z12">
+        <v>0.338015752659114</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.05744379875142541</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05744379875142541</v>
+      </c>
+      <c r="AD12">
+        <v>47808.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>47808.5</v>
+      </c>
+      <c r="AG12">
+        <v>40262.2</v>
+      </c>
+      <c r="AH12">
+        <v>0.9456318783476934</v>
+      </c>
+      <c r="AI12">
+        <v>0.8701900062431402</v>
+      </c>
+      <c r="AJ12">
+        <v>0.9360929438816673</v>
+      </c>
+      <c r="AK12">
+        <v>0.8495210364181119</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Daishin Securities Co.,Ltd (KOSE:A003540)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.0407</v>
+      </c>
+      <c r="E13">
+        <v>0.0316</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>75.8</v>
+      </c>
+      <c r="L13">
+        <v>0.03323978249429924</v>
+      </c>
+      <c r="M13">
+        <v>62.5</v>
+      </c>
+      <c r="N13">
+        <v>0.08662508662508663</v>
+      </c>
+      <c r="O13">
+        <v>0.8245382585751979</v>
+      </c>
+      <c r="P13">
+        <v>62.5</v>
+      </c>
+      <c r="Q13">
+        <v>0.08662508662508663</v>
+      </c>
+      <c r="R13">
+        <v>0.8245382585751979</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1471.5</v>
+      </c>
+      <c r="V13">
+        <v>2.039501039501039</v>
+      </c>
+      <c r="W13">
+        <v>0.03674082691095924</v>
+      </c>
+      <c r="X13">
+        <v>0.2987504435389162</v>
+      </c>
+      <c r="Y13">
+        <v>-0.2620096166279569</v>
+      </c>
+      <c r="Z13">
+        <v>0.2364505459183144</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.05747636528224469</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05747636528224469</v>
+      </c>
+      <c r="AD13">
+        <v>11636.6</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>11636.6</v>
+      </c>
+      <c r="AG13">
+        <v>10165.1</v>
+      </c>
+      <c r="AH13">
+        <v>0.9416172388959468</v>
+      </c>
+      <c r="AI13">
+        <v>0.8232589070945469</v>
+      </c>
+      <c r="AJ13">
+        <v>0.9337258648246468</v>
+      </c>
+      <c r="AK13">
+        <v>0.8027212495952872</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kyobo Securities Co.,Ltd. (KOSE:A030610)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.168</v>
+      </c>
+      <c r="E14">
+        <v>0.108</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>107</v>
+      </c>
+      <c r="L14">
+        <v>0.05047407896598896</v>
+      </c>
+      <c r="M14">
+        <v>21.451</v>
+      </c>
+      <c r="N14">
+        <v>0.05048481995763709</v>
+      </c>
+      <c r="O14">
+        <v>0.2004766355140187</v>
+      </c>
+      <c r="P14">
+        <v>21.451</v>
+      </c>
+      <c r="Q14">
+        <v>0.05048481995763709</v>
+      </c>
+      <c r="R14">
+        <v>0.2004766355140187</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>109.3</v>
+      </c>
+      <c r="V14">
+        <v>0.2572369969404566</v>
+      </c>
+      <c r="W14">
+        <v>0.07716717149862974</v>
+      </c>
+      <c r="X14">
+        <v>0.2547082216444137</v>
+      </c>
+      <c r="Y14">
+        <v>-0.177541050145784</v>
+      </c>
+      <c r="Z14">
+        <v>0.3187771612456956</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.05757857197269398</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05757857197269398</v>
+      </c>
+      <c r="AD14">
+        <v>5561.1</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>5561.1</v>
+      </c>
+      <c r="AG14">
+        <v>5451.8</v>
+      </c>
+      <c r="AH14">
+        <v>0.9290177079852991</v>
+      </c>
+      <c r="AI14">
+        <v>0.7850669151279011</v>
+      </c>
+      <c r="AJ14">
+        <v>0.927697517314139</v>
+      </c>
+      <c r="AK14">
+        <v>0.781698521715441</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Samsung Securities Co.,Ltd. (KOSE:A016360)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.123</v>
+      </c>
+      <c r="E15">
+        <v>0.17</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>566.1</v>
+      </c>
+      <c r="L15">
+        <v>0.07263279445727483</v>
+      </c>
+      <c r="M15">
+        <v>150.024</v>
+      </c>
+      <c r="N15">
+        <v>0.05704768423454255</v>
+      </c>
+      <c r="O15">
+        <v>0.2650132485426603</v>
+      </c>
+      <c r="P15">
+        <v>150.024</v>
+      </c>
+      <c r="Q15">
+        <v>0.05704768423454255</v>
+      </c>
+      <c r="R15">
+        <v>0.2650132485426603</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>1855.3</v>
+      </c>
+      <c r="V15">
+        <v>0.7054909118564149</v>
+      </c>
+      <c r="W15">
+        <v>0.114609061829372</v>
+      </c>
+      <c r="X15">
+        <v>0.1676863848833445</v>
+      </c>
+      <c r="Y15">
+        <v>-0.05307732305397253</v>
+      </c>
+      <c r="Z15">
+        <v>0.3852237005990392</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.05800663054738192</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05800663054738192</v>
+      </c>
+      <c r="AD15">
+        <v>18620.9</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>18620.9</v>
+      </c>
+      <c r="AG15">
+        <v>16765.6</v>
+      </c>
+      <c r="AH15">
+        <v>0.8762487823930506</v>
+      </c>
+      <c r="AI15">
+        <v>0.7735341156921799</v>
+      </c>
+      <c r="AJ15">
+        <v>0.8644111490353383</v>
+      </c>
+      <c r="AK15">
+        <v>0.754622544695101</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shinyoung Securities Co., Ltd. (KOSE:A001720)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.06269999999999999</v>
+      </c>
+      <c r="E16">
+        <v>0.225</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>105.5</v>
+      </c>
+      <c r="L16">
+        <v>0.06143006870851286</v>
+      </c>
+      <c r="M16">
+        <v>31.8</v>
+      </c>
+      <c r="N16">
+        <v>0.04735666418466121</v>
+      </c>
+      <c r="O16">
+        <v>0.3014218009478673</v>
+      </c>
+      <c r="P16">
+        <v>31.8</v>
+      </c>
+      <c r="Q16">
+        <v>0.04735666418466121</v>
+      </c>
+      <c r="R16">
+        <v>0.3014218009478673</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>247.5</v>
+      </c>
+      <c r="V16">
+        <v>0.3685778108711839</v>
+      </c>
+      <c r="W16">
+        <v>0.09345380458853751</v>
+      </c>
+      <c r="X16">
+        <v>0.160616828569436</v>
+      </c>
+      <c r="Y16">
+        <v>-0.06716302398089848</v>
+      </c>
+      <c r="Z16">
+        <v>0.3612992805149998</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.05807115445912351</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05807115445912351</v>
+      </c>
+      <c r="AD16">
+        <v>4427</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>4427</v>
+      </c>
+      <c r="AG16">
+        <v>4179.5</v>
+      </c>
+      <c r="AH16">
+        <v>0.8682945964499362</v>
+      </c>
+      <c r="AI16">
+        <v>0.7664208303036598</v>
+      </c>
+      <c r="AJ16">
+        <v>0.8615749330035044</v>
+      </c>
+      <c r="AK16">
+        <v>0.7559643315788522</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hanyang Securities Co. Ltd. (KOSE:A001750)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.243</v>
+      </c>
+      <c r="E17">
+        <v>0.192</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>31</v>
+      </c>
+      <c r="L17">
+        <v>0.05448154657293498</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>-0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>216.3</v>
+      </c>
+      <c r="V17">
+        <v>2.137351778656126</v>
+      </c>
+      <c r="W17">
+        <v>0.08717660292463442</v>
+      </c>
+      <c r="X17">
+        <v>0.4747173364266328</v>
+      </c>
+      <c r="Y17">
+        <v>-0.3875407335019984</v>
+      </c>
+      <c r="Z17">
+        <v>0.4286413800896455</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.05981519079727975</v>
+      </c>
+      <c r="AC17">
+        <v>-0.05981519079727975</v>
+      </c>
+      <c r="AD17">
+        <v>2861.5</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>2861.5</v>
+      </c>
+      <c r="AG17">
+        <v>2645.2</v>
+      </c>
+      <c r="AH17">
+        <v>0.9658419684747022</v>
+      </c>
+      <c r="AI17">
+        <v>0.8807867520315192</v>
+      </c>
+      <c r="AJ17">
+        <v>0.9631517623070202</v>
+      </c>
+      <c r="AK17">
+        <v>0.8722835943940642</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Eugene Investment &amp; Securities Co.,Ltd. (KOSE:A001200)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0873</v>
+      </c>
+      <c r="E18">
+        <v>0.0247</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>36.9</v>
+      </c>
+      <c r="L18">
+        <v>0.03520992366412214</v>
+      </c>
+      <c r="M18">
+        <v>4.222799999999999</v>
+      </c>
+      <c r="N18">
+        <v>0.02789167767503302</v>
+      </c>
+      <c r="O18">
+        <v>0.1144390243902439</v>
+      </c>
+      <c r="P18">
+        <v>4.222799999999999</v>
+      </c>
+      <c r="Q18">
+        <v>0.02789167767503302</v>
+      </c>
+      <c r="R18">
+        <v>0.1144390243902439</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>320.5</v>
+      </c>
+      <c r="V18">
+        <v>2.116908850726552</v>
+      </c>
+      <c r="W18">
+        <v>0.049338146811071</v>
+      </c>
+      <c r="X18">
+        <v>0.4234957425780241</v>
+      </c>
+      <c r="Y18">
+        <v>-0.3741575957669531</v>
+      </c>
+      <c r="Z18">
+        <v>0.2904656319290466</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.05984093754841265</v>
+      </c>
+      <c r="AC18">
+        <v>-0.05984093754841265</v>
+      </c>
+      <c r="AD18">
+        <v>3745.6</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>3745.6</v>
+      </c>
+      <c r="AG18">
+        <v>3425.1</v>
+      </c>
+      <c r="AH18">
+        <v>0.9611496022581473</v>
+      </c>
+      <c r="AI18">
+        <v>0.8246950548240785</v>
+      </c>
+      <c r="AJ18">
+        <v>0.9576681112819796</v>
+      </c>
+      <c r="AK18">
+        <v>0.8113851183284769</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Yuhwa Securities co.,ltd. (KOSE:A003460)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.13</v>
+      </c>
+      <c r="E19">
+        <v>0.337</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>17.9</v>
+      </c>
+      <c r="L19">
+        <v>0.7075098814229248</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
+        <v>-0</v>
+      </c>
+      <c r="O19">
+        <v>-0</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>-0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0.465</v>
+      </c>
+      <c r="V19">
+        <v>0.006690647482014389</v>
+      </c>
+      <c r="W19">
+        <v>0.0499581356405247</v>
+      </c>
+      <c r="X19">
+        <v>0.09150222067983084</v>
+      </c>
+      <c r="Y19">
+        <v>-0.04154408503930614</v>
+      </c>
+      <c r="Z19">
+        <v>0.0573826264459061</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.05987772992852589</v>
+      </c>
+      <c r="AC19">
+        <v>-0.05987772992852589</v>
+      </c>
+      <c r="AD19">
+        <v>126.6</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>126.6</v>
+      </c>
+      <c r="AG19">
+        <v>126.135</v>
+      </c>
+      <c r="AH19">
+        <v>0.6455889852116267</v>
+      </c>
+      <c r="AI19">
+        <v>0.2454915648632926</v>
+      </c>
+      <c r="AJ19">
+        <v>0.6447465944232883</v>
+      </c>
+      <c r="AK19">
+        <v>0.2448106203965181</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hanwha Investment &amp; Securities Co., Ltd. (KOSE:A003530)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>-0.00411</v>
+      </c>
+      <c r="E20">
+        <v>-0.0842</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>36.1</v>
+      </c>
+      <c r="L20">
+        <v>0.03048986486486487</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>-0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>183.5</v>
+      </c>
+      <c r="V20">
+        <v>0.3628633577219695</v>
+      </c>
+      <c r="W20">
+        <v>0.031011081522206</v>
+      </c>
+      <c r="X20">
+        <v>0.2270191270527448</v>
+      </c>
+      <c r="Y20">
+        <v>-0.1960080455305388</v>
+      </c>
+      <c r="Z20">
+        <v>0.1984039873839195</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.06007838188069162</v>
+      </c>
+      <c r="AC20">
+        <v>-0.06007838188069162</v>
+      </c>
+      <c r="AD20">
+        <v>5652</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>5652</v>
+      </c>
+      <c r="AG20">
+        <v>5468.5</v>
+      </c>
+      <c r="AH20">
+        <v>0.9178751806681066</v>
+      </c>
+      <c r="AI20">
+        <v>0.8176610149875586</v>
+      </c>
+      <c r="AJ20">
+        <v>0.9153526832044458</v>
+      </c>
+      <c r="AK20">
+        <v>0.8126885523636851</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kiwoom Securities Co., Ltd. (KOSE:A039490)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.256</v>
+      </c>
+      <c r="E21">
+        <v>0.14</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>378.8</v>
+      </c>
+      <c r="L21">
+        <v>0.07000683804912307</v>
+      </c>
+      <c r="M21">
+        <v>151.7</v>
+      </c>
+      <c r="N21">
+        <v>0.07237940741447588</v>
+      </c>
+      <c r="O21">
+        <v>0.4004751847940866</v>
+      </c>
+      <c r="P21">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="Q21">
+        <v>0.03201488620640297</v>
+      </c>
+      <c r="R21">
+        <v>0.1771383315733896</v>
+      </c>
+      <c r="S21">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="T21">
+        <v>0.5576796308503625</v>
+      </c>
+      <c r="U21">
+        <v>918.1</v>
+      </c>
+      <c r="V21">
+        <v>0.4380457082876091</v>
+      </c>
+      <c r="W21">
+        <v>0.1002620364733596</v>
+      </c>
+      <c r="X21">
+        <v>0.1929718089011635</v>
+      </c>
+      <c r="Y21">
+        <v>-0.09270977242780387</v>
+      </c>
+      <c r="Z21">
+        <v>0.3196023650185173</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.06018616515124298</v>
+      </c>
+      <c r="AC21">
+        <v>-0.06018616515124298</v>
+      </c>
+      <c r="AD21">
+        <v>18498.9</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>18498.9</v>
+      </c>
+      <c r="AG21">
+        <v>17580.8</v>
+      </c>
+      <c r="AH21">
+        <v>0.8982315924408103</v>
+      </c>
+      <c r="AI21">
+        <v>0.8158459943989945</v>
+      </c>
+      <c r="AJ21">
+        <v>0.8934831552038706</v>
+      </c>
+      <c r="AK21">
+        <v>0.8080748653269844</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Korea Asset Investment Securities Co., Ltd. (KOSDAQ:A190650)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>5.93</v>
+      </c>
+      <c r="L22">
+        <v>0.03342728297632469</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>-0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>-0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>15.3</v>
+      </c>
+      <c r="V22">
+        <v>0.6455696202531646</v>
+      </c>
+      <c r="W22">
+        <v>0.08971255673222391</v>
+      </c>
+      <c r="X22">
+        <v>0.1788025716302554</v>
+      </c>
+      <c r="Y22">
+        <v>-0.08909001489803149</v>
+      </c>
+      <c r="Z22">
+        <v>2.578488372093024</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.06024789431730455</v>
+      </c>
+      <c r="AC22">
+        <v>-0.06024789431730455</v>
+      </c>
+      <c r="AD22">
+        <v>186</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>186</v>
+      </c>
+      <c r="AG22">
+        <v>170.7</v>
+      </c>
+      <c r="AH22">
+        <v>0.8869814020028612</v>
+      </c>
+      <c r="AI22">
+        <v>0.7228915662650602</v>
+      </c>
+      <c r="AJ22">
+        <v>0.8780864197530864</v>
+      </c>
+      <c r="AK22">
+        <v>0.7053719008264462</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>NH Investment &amp; Securities Co., Ltd. (KOSE:A005940)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D23">
         <v>-0.06370000000000001</v>
       </c>
-      <c r="E3">
+      <c r="E23">
         <v>0.125</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>506.7</v>
       </c>
-      <c r="L3">
+      <c r="L23">
         <v>0.07490243614001892</v>
       </c>
-      <c r="M3">
+      <c r="M23">
         <v>251.6</v>
       </c>
-      <c r="N3">
+      <c r="N23">
         <v>0.07761120365229193</v>
       </c>
-      <c r="O3">
+      <c r="O23">
         <v>0.4965462798500099</v>
       </c>
-      <c r="P3">
+      <c r="P23">
         <v>212.4</v>
       </c>
-      <c r="Q3">
+      <c r="Q23">
         <v>0.06551915602443087</v>
       </c>
-      <c r="R3">
+      <c r="R23">
         <v>0.4191829484902309</v>
       </c>
-      <c r="S3">
+      <c r="S23">
         <v>39.20000000000002</v>
       </c>
-      <c r="T3">
+      <c r="T23">
         <v>0.1558028616852147</v>
       </c>
-      <c r="U3">
+      <c r="U23">
         <v>2211.1</v>
       </c>
-      <c r="V3">
+      <c r="V23">
         <v>0.6820593497439693</v>
       </c>
-      <c r="W3">
+      <c r="W23">
         <v>0.09038691378725985</v>
       </c>
-      <c r="X3">
-        <v>0.1606542382405337</v>
-      </c>
-      <c r="Y3">
-        <v>-0.0702673244532738</v>
-      </c>
-      <c r="Z3">
+      <c r="X23">
+        <v>0.160597505483689</v>
+      </c>
+      <c r="Y23">
+        <v>-0.07021059169642913</v>
+      </c>
+      <c r="Z23">
         <v>0.3345995568217791</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.06035802808004222</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06035802808004222</v>
-      </c>
-      <c r="AD3">
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.06035055475646904</v>
+      </c>
+      <c r="AC23">
+        <v>-0.06035055475646904</v>
+      </c>
+      <c r="AD23">
         <v>21367.9</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
         <v>21367.9</v>
       </c>
-      <c r="AG3">
+      <c r="AG23">
         <v>19156.8</v>
       </c>
-      <c r="AH3">
+      <c r="AH23">
         <v>0.868271453938894</v>
       </c>
-      <c r="AI3">
+      <c r="AI23">
         <v>0.7803601622958064</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ23">
         <v>0.8552677399480325</v>
       </c>
-      <c r="AK3">
+      <c r="AK23">
         <v>0.7610663064637877</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Daol Investment &amp; Securities Co., Ltd. (KOSE:A030210)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.224</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-19.3</v>
+      </c>
+      <c r="L24">
+        <v>-0.02811361981063365</v>
+      </c>
+      <c r="M24">
+        <v>6.9718</v>
+      </c>
+      <c r="N24">
+        <v>0.05546380270485282</v>
+      </c>
+      <c r="O24">
+        <v>-0.3612331606217616</v>
+      </c>
+      <c r="P24">
+        <v>6.7488</v>
+      </c>
+      <c r="Q24">
+        <v>0.05368973747016707</v>
+      </c>
+      <c r="R24">
+        <v>-0.3496787564766839</v>
+      </c>
+      <c r="S24">
+        <v>0.2229999999999999</v>
+      </c>
+      <c r="T24">
+        <v>0.03198600074586188</v>
+      </c>
+      <c r="U24">
+        <v>549.4</v>
+      </c>
+      <c r="V24">
+        <v>4.370723945902943</v>
+      </c>
+      <c r="W24">
+        <v>-0.04666344294003869</v>
+      </c>
+      <c r="X24">
+        <v>0.4364388914799665</v>
+      </c>
+      <c r="Y24">
+        <v>-0.4831023344200052</v>
+      </c>
+      <c r="Z24">
+        <v>0.2621529766678123</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.06163838541836475</v>
+      </c>
+      <c r="AC24">
+        <v>-0.06163838541836475</v>
+      </c>
+      <c r="AD24">
+        <v>3222.1</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>3222.1</v>
+      </c>
+      <c r="AG24">
+        <v>2672.7</v>
+      </c>
+      <c r="AH24">
+        <v>0.9624529541788638</v>
+      </c>
+      <c r="AI24">
+        <v>0.8411915204678363</v>
+      </c>
+      <c r="AJ24">
+        <v>0.9550814751286451</v>
+      </c>
+      <c r="AK24">
+        <v>0.8145992075586711</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
         <v>0</v>
       </c>
     </row>
